--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130158974</v>
       </c>
       <c r="B2" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,225 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132082678</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Morby, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>657589</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6629798</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132082680</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91861</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Morby, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>657538</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629769</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>132082680</v>
       </c>
       <c r="B4" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>132082680</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132229123</v>
       </c>
       <c r="B6" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132229125</v>
+        <v>132229129</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>92615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657566</v>
+        <v>657617</v>
       </c>
       <c r="R12" t="n">
-        <v>6629737</v>
+        <v>6629722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1865,7 @@
         <v>132229117</v>
       </c>
       <c r="B13" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,32 +1969,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132229129</v>
+        <v>132229125</v>
       </c>
       <c r="B14" t="n">
-        <v>92612</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657617</v>
+        <v>657566</v>
       </c>
       <c r="R14" t="n">
-        <v>6629722</v>
+        <v>6629737</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,45 +2081,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B15" t="n">
-        <v>4781</v>
+        <v>92312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R15" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2154,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2164,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,6 +2173,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,48 +2192,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>4781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R16" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2271,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132229131</v>
+        <v>132229113</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657670</v>
+        <v>657681</v>
       </c>
       <c r="R17" t="n">
-        <v>6629756</v>
+        <v>6629873</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132229113</v>
+        <v>132229131</v>
       </c>
       <c r="B18" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657681</v>
+        <v>657670</v>
       </c>
       <c r="R18" t="n">
-        <v>6629873</v>
+        <v>6629756</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132229112</v>
+        <v>132229110</v>
       </c>
       <c r="B19" t="n">
-        <v>91889</v>
+        <v>97338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657675</v>
+        <v>657640</v>
       </c>
       <c r="R19" t="n">
-        <v>6629888</v>
+        <v>6629986</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132229110</v>
+        <v>132229112</v>
       </c>
       <c r="B20" t="n">
-        <v>97335</v>
+        <v>91892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657640</v>
+        <v>657675</v>
       </c>
       <c r="R20" t="n">
-        <v>6629986</v>
+        <v>6629888</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,7 +2837,7 @@
         <v>132229122</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132229104</v>
       </c>
       <c r="B23" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132229106</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,32 +3151,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132229135</v>
+        <v>132229105</v>
       </c>
       <c r="B25" t="n">
-        <v>4781</v>
+        <v>97338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>657669</v>
+        <v>657629</v>
       </c>
       <c r="R25" t="n">
-        <v>6629815</v>
+        <v>6629952</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,32 +3258,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132229105</v>
+        <v>132229135</v>
       </c>
       <c r="B26" t="n">
-        <v>97335</v>
+        <v>4781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>657629</v>
+        <v>657669</v>
       </c>
       <c r="R26" t="n">
-        <v>6629952</v>
+        <v>6629815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3368,7 @@
         <v>132229107</v>
       </c>
       <c r="B27" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>132229118</v>
       </c>
       <c r="B28" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303809</v>
+        <v>132303827</v>
       </c>
       <c r="B29" t="n">
-        <v>92612</v>
+        <v>91892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657556</v>
+        <v>657470</v>
       </c>
       <c r="R29" t="n">
-        <v>6629205</v>
+        <v>6629072</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303827</v>
+        <v>132303818</v>
       </c>
       <c r="B30" t="n">
-        <v>91889</v>
+        <v>92352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657470</v>
+        <v>657503</v>
       </c>
       <c r="R30" t="n">
-        <v>6629072</v>
+        <v>6629178</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3793,32 +3793,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132303818</v>
+        <v>132303809</v>
       </c>
       <c r="B31" t="n">
-        <v>92349</v>
+        <v>92615</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657503</v>
+        <v>657556</v>
       </c>
       <c r="R31" t="n">
-        <v>6629178</v>
+        <v>6629205</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132303836</v>
+        <v>132303811</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>657418</v>
+        <v>657543</v>
       </c>
       <c r="R32" t="n">
-        <v>6629375</v>
+        <v>6629159</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132303811</v>
+        <v>132303836</v>
       </c>
       <c r="B33" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>657543</v>
+        <v>657418</v>
       </c>
       <c r="R33" t="n">
-        <v>6629159</v>
+        <v>6629375</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,7 +4117,7 @@
         <v>132303832</v>
       </c>
       <c r="B34" t="n">
-        <v>92313</v>
+        <v>92316</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>132303803</v>
       </c>
       <c r="B35" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>132303822</v>
       </c>
       <c r="B36" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>132303789</v>
       </c>
       <c r="B37" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,32 +4543,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132303821</v>
+        <v>132303815</v>
       </c>
       <c r="B38" t="n">
-        <v>97335</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>657531</v>
+        <v>657525</v>
       </c>
       <c r="R38" t="n">
-        <v>6629123</v>
+        <v>6629176</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4650,32 +4650,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132303815</v>
+        <v>132303821</v>
       </c>
       <c r="B39" t="n">
-        <v>92349</v>
+        <v>97338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>657525</v>
+        <v>657531</v>
       </c>
       <c r="R39" t="n">
-        <v>6629176</v>
+        <v>6629123</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132303810</v>
+        <v>132303788</v>
       </c>
       <c r="B40" t="n">
-        <v>101301</v>
+        <v>5179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657560</v>
+        <v>657609</v>
       </c>
       <c r="R40" t="n">
-        <v>6629165</v>
+        <v>6629874</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132303788</v>
+        <v>132303810</v>
       </c>
       <c r="B41" t="n">
-        <v>5179</v>
+        <v>101304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657609</v>
+        <v>657560</v>
       </c>
       <c r="R41" t="n">
-        <v>6629874</v>
+        <v>6629165</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4971,32 +4971,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132303817</v>
+        <v>132303785</v>
       </c>
       <c r="B42" t="n">
-        <v>92349</v>
+        <v>97338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657521</v>
+        <v>657626</v>
       </c>
       <c r="R42" t="n">
-        <v>6629192</v>
+        <v>6629945</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5078,10 +5078,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132303833</v>
+        <v>132303817</v>
       </c>
       <c r="B43" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>657443</v>
+        <v>657521</v>
       </c>
       <c r="R43" t="n">
-        <v>6629220</v>
+        <v>6629192</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132303785</v>
+        <v>132303833</v>
       </c>
       <c r="B44" t="n">
-        <v>97335</v>
+        <v>92352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657626</v>
+        <v>657443</v>
       </c>
       <c r="R44" t="n">
-        <v>6629945</v>
+        <v>6629220</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5407,7 +5407,7 @@
         <v>132303808</v>
       </c>
       <c r="B46" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>132303804</v>
       </c>
       <c r="B49" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>132303819</v>
       </c>
       <c r="B50" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5944,10 +5944,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303823</v>
+        <v>132303813</v>
       </c>
       <c r="B51" t="n">
-        <v>97335</v>
+        <v>91892</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657524</v>
+        <v>657528</v>
       </c>
       <c r="R51" t="n">
-        <v>6629112</v>
+        <v>6629154</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303834</v>
+        <v>132303816</v>
       </c>
       <c r="B52" t="n">
-        <v>4781</v>
+        <v>92352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657418</v>
+        <v>657523</v>
       </c>
       <c r="R52" t="n">
-        <v>6629221</v>
+        <v>6629179</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303793</v>
+        <v>132303823</v>
       </c>
       <c r="B53" t="n">
-        <v>5199</v>
+        <v>97338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657601</v>
+        <v>657524</v>
       </c>
       <c r="R53" t="n">
-        <v>6629629</v>
+        <v>6629112</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303813</v>
+        <v>132303834</v>
       </c>
       <c r="B54" t="n">
-        <v>91889</v>
+        <v>4781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657528</v>
+        <v>657418</v>
       </c>
       <c r="R54" t="n">
-        <v>6629154</v>
+        <v>6629221</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,32 +6372,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303816</v>
+        <v>132303793</v>
       </c>
       <c r="B55" t="n">
-        <v>92349</v>
+        <v>5199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657523</v>
+        <v>657601</v>
       </c>
       <c r="R55" t="n">
-        <v>6629179</v>
+        <v>6629629</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,32 +6479,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132303797</v>
+        <v>132303791</v>
       </c>
       <c r="B56" t="n">
-        <v>92114</v>
+        <v>4781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1106</v>
+        <v>102306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>657663</v>
+        <v>657605</v>
       </c>
       <c r="R56" t="n">
-        <v>6629597</v>
+        <v>6629850</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6586,32 +6586,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132303791</v>
+        <v>132303797</v>
       </c>
       <c r="B57" t="n">
-        <v>4781</v>
+        <v>92117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102306</v>
+        <v>1106</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657605</v>
+        <v>657663</v>
       </c>
       <c r="R57" t="n">
-        <v>6629850</v>
+        <v>6629597</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,7 +6696,7 @@
         <v>132303835</v>
       </c>
       <c r="B58" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>132303828</v>
       </c>
       <c r="B61" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7117,10 +7117,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132303805</v>
+        <v>132303802</v>
       </c>
       <c r="B62" t="n">
-        <v>97335</v>
+        <v>57945</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,21 +7128,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>657549</v>
+        <v>657568</v>
       </c>
       <c r="R62" t="n">
-        <v>6629245</v>
+        <v>6629349</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7197,7 +7197,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7224,7 +7229,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303802</v>
+        <v>132303801</v>
       </c>
       <c r="B63" t="n">
         <v>57945</v>
@@ -7259,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>657568</v>
+        <v>657607</v>
       </c>
       <c r="R63" t="n">
-        <v>6629349</v>
+        <v>6629402</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,7 +7299,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7304,7 +7309,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7336,32 +7341,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132303801</v>
+        <v>132303792</v>
       </c>
       <c r="B64" t="n">
-        <v>57945</v>
+        <v>4781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7374,7 +7379,7 @@
         <v>657607</v>
       </c>
       <c r="R64" t="n">
-        <v>6629402</v>
+        <v>6629839</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7406,7 +7411,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7416,12 +7421,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,32 +7448,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303792</v>
+        <v>132303805</v>
       </c>
       <c r="B65" t="n">
-        <v>4781</v>
+        <v>97338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>657607</v>
+        <v>657549</v>
       </c>
       <c r="R65" t="n">
-        <v>6629839</v>
+        <v>6629245</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,7 +7558,7 @@
         <v>132303826</v>
       </c>
       <c r="B66" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>132303800</v>
       </c>
       <c r="B67" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132303814</v>
       </c>
       <c r="B68" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8319,10 +8319,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132393747</v>
+        <v>132398523</v>
       </c>
       <c r="B73" t="n">
-        <v>91852</v>
+        <v>79341</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8330,37 +8330,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657641</v>
+        <v>657569</v>
       </c>
       <c r="R73" t="n">
-        <v>6629957</v>
+        <v>6629311</v>
       </c>
       <c r="S73" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,39 +8390,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8429,7 +8448,7 @@
         <v>132395560</v>
       </c>
       <c r="B74" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8543,10 +8562,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132398523</v>
+        <v>132393747</v>
       </c>
       <c r="B75" t="n">
-        <v>79339</v>
+        <v>91855</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8554,40 +8573,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657569</v>
+        <v>657641</v>
       </c>
       <c r="R75" t="n">
-        <v>6629311</v>
+        <v>6629957</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8614,65 +8630,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132393759</v>
+        <v>132397152</v>
       </c>
       <c r="B76" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8698,19 +8698,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>657538</v>
+        <v>657580</v>
       </c>
       <c r="R76" t="n">
-        <v>6629440</v>
+        <v>6629659</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8737,49 +8740,60 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132397152</v>
+        <v>132393759</v>
       </c>
       <c r="B77" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8805,22 +8819,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>657580</v>
+        <v>657538</v>
       </c>
       <c r="R77" t="n">
-        <v>6629659</v>
+        <v>6629440</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8847,50 +8858,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8900,7 +8900,7 @@
         <v>132393767</v>
       </c>
       <c r="B78" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9004,10 +9004,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132398009</v>
+        <v>132395803</v>
       </c>
       <c r="B79" t="n">
-        <v>91852</v>
+        <v>97658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9015,26 +9015,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>2326</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9042,10 +9043,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657441</v>
+        <v>657653</v>
       </c>
       <c r="R79" t="n">
-        <v>6629193</v>
+        <v>6629952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9086,28 +9087,12 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9118,17 +9103,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132395803</v>
+        <v>132398009</v>
       </c>
       <c r="B80" t="n">
-        <v>97655</v>
+        <v>91855</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9136,27 +9121,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2326</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9164,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657653</v>
+        <v>657441</v>
       </c>
       <c r="R80" t="n">
-        <v>6629952</v>
+        <v>6629193</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,12 +9192,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9234,7 +9234,7 @@
         <v>132393769</v>
       </c>
       <c r="B81" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9338,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393768</v>
+        <v>132393780</v>
       </c>
       <c r="B82" t="n">
-        <v>91889</v>
+        <v>91912</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9349,23 +9349,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9373,10 +9369,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657498</v>
+        <v>657500</v>
       </c>
       <c r="R82" t="n">
-        <v>6629248</v>
+        <v>6629450</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9408,7 +9404,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9418,7 +9414,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9445,10 +9441,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132393780</v>
+        <v>132393768</v>
       </c>
       <c r="B83" t="n">
-        <v>91909</v>
+        <v>91892</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9456,19 +9452,23 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657500</v>
+        <v>657498</v>
       </c>
       <c r="R83" t="n">
-        <v>6629450</v>
+        <v>6629248</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9670,10 +9670,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132393770</v>
+        <v>132397799</v>
       </c>
       <c r="B85" t="n">
-        <v>8444</v>
+        <v>92547</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,37 +9681,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657487</v>
+        <v>657535</v>
       </c>
       <c r="R85" t="n">
-        <v>6629134</v>
+        <v>6629432</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9738,49 +9741,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132398283</v>
+        <v>132393770</v>
       </c>
       <c r="B86" t="n">
-        <v>106219</v>
+        <v>8444</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9788,41 +9807,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657575</v>
+        <v>657487</v>
       </c>
       <c r="R86" t="n">
-        <v>6629279</v>
+        <v>6629134</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9849,40 +9864,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B87" t="n">
-        <v>92544</v>
+        <v>106222</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9890,26 +9914,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9917,10 +9942,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R87" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9964,31 +9989,6 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10005,10 +10005,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132400287</v>
+        <v>132398041</v>
       </c>
       <c r="B88" t="n">
-        <v>101301</v>
+        <v>9414</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10016,38 +10016,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>105076</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657564</v>
+        <v>657485</v>
       </c>
       <c r="R88" t="n">
-        <v>6629426</v>
+        <v>6629132</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10077,19 +10078,9 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10102,15 +10093,40 @@
       <c r="AG88" t="b">
         <v>0</v>
       </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+        </is>
+      </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10120,7 +10136,7 @@
         <v>132393760</v>
       </c>
       <c r="B89" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10224,10 +10240,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132393762</v>
+        <v>132393758</v>
       </c>
       <c r="B90" t="n">
-        <v>97335</v>
+        <v>91892</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10235,21 +10251,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10275,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657575</v>
+        <v>657570</v>
       </c>
       <c r="R90" t="n">
-        <v>6629363</v>
+        <v>6629495</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10310,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10320,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,48 +10347,52 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132393758</v>
+        <v>132400287</v>
       </c>
       <c r="B91" t="n">
-        <v>91889</v>
+        <v>101304</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657570</v>
+        <v>657564</v>
       </c>
       <c r="R91" t="n">
-        <v>6629495</v>
+        <v>6629426</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10401,7 +10421,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10431,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10420,71 +10440,67 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132398041</v>
+        <v>132393762</v>
       </c>
       <c r="B92" t="n">
-        <v>9414</v>
+        <v>97338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>105076</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>657485</v>
+        <v>657575</v>
       </c>
       <c r="R92" t="n">
-        <v>6629132</v>
+        <v>6629363</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10511,65 +10527,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132398032</v>
+        <v>132397298</v>
       </c>
       <c r="B93" t="n">
-        <v>8444</v>
+        <v>92316</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10577,32 +10577,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106554</v>
+        <v>4217</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10610,10 +10604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657485</v>
+        <v>657657</v>
       </c>
       <c r="R93" t="n">
-        <v>6629132</v>
+        <v>6629610</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10660,27 +10654,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10698,32 +10692,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132397298</v>
+        <v>132397367</v>
       </c>
       <c r="B94" t="n">
-        <v>92313</v>
+        <v>91814</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4217</v>
+        <v>3242</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10736,10 +10730,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657657</v>
+        <v>657627</v>
       </c>
       <c r="R94" t="n">
-        <v>6629610</v>
+        <v>6629577</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,12 +10795,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10824,37 +10818,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132397367</v>
+        <v>132398032</v>
       </c>
       <c r="B95" t="n">
-        <v>91811</v>
+        <v>8444</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3242</v>
+        <v>106554</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657627</v>
+        <v>657485</v>
       </c>
       <c r="R95" t="n">
-        <v>6629577</v>
+        <v>6629132</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10912,27 +10912,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10950,32 +10950,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132393772</v>
+        <v>132393773</v>
       </c>
       <c r="B96" t="n">
-        <v>101301</v>
+        <v>91892</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657497</v>
+        <v>657548</v>
       </c>
       <c r="R96" t="n">
-        <v>6629103</v>
+        <v>6629166</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11057,10 +11057,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132393773</v>
+        <v>132400285</v>
       </c>
       <c r="B97" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11086,19 +11086,22 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657548</v>
+        <v>657528</v>
       </c>
       <c r="R97" t="n">
-        <v>6629166</v>
+        <v>6629248</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11127,7 +11130,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11137,7 +11140,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11146,18 +11154,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11167,7 +11176,7 @@
         <v>132400283</v>
       </c>
       <c r="B98" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11271,48 +11280,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132400285</v>
+        <v>132398021</v>
       </c>
       <c r="B99" t="n">
-        <v>91889</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657528</v>
+        <v>657497</v>
       </c>
       <c r="R99" t="n">
-        <v>6629248</v>
+        <v>6629177</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11342,24 +11357,9 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11372,25 +11372,50 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132398021</v>
+        <v>132393772</v>
       </c>
       <c r="B100" t="n">
-        <v>8455</v>
+        <v>101304</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11398,33 +11423,24 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
@@ -11434,10 +11450,10 @@
         <v>657497</v>
       </c>
       <c r="R100" t="n">
-        <v>6629177</v>
+        <v>6629103</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11464,103 +11480,90 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132393776</v>
+        <v>132396638</v>
       </c>
       <c r="B101" t="n">
-        <v>101301</v>
+        <v>92191</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657575</v>
+        <v>657608</v>
       </c>
       <c r="R101" t="n">
-        <v>6629232</v>
+        <v>6629860</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11587,21 +11590,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11610,53 +11603,80 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132396638</v>
+        <v>132396920</v>
       </c>
       <c r="B102" t="n">
-        <v>92188</v>
+        <v>4775</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11664,10 +11684,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657608</v>
+        <v>657583</v>
       </c>
       <c r="R102" t="n">
-        <v>6629860</v>
+        <v>6629810</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11713,7 +11733,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -11726,14 +11746,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11751,10 +11766,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B103" t="n">
-        <v>4775</v>
+        <v>101304</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11762,42 +11777,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R103" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11824,11 +11834,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11837,36 +11857,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11876,7 +11876,7 @@
         <v>132400288</v>
       </c>
       <c r="B104" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>132393753</v>
       </c>
       <c r="B105" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12096,32 +12096,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393761</v>
+        <v>132393751</v>
       </c>
       <c r="B106" t="n">
-        <v>101301</v>
+        <v>91892</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657545</v>
+        <v>657577</v>
       </c>
       <c r="R106" t="n">
-        <v>6629427</v>
+        <v>6629624</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12203,10 +12203,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132393751</v>
+        <v>132393766</v>
       </c>
       <c r="B107" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657577</v>
+        <v>657539</v>
       </c>
       <c r="R107" t="n">
-        <v>6629624</v>
+        <v>6629301</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393766</v>
+        <v>132393761</v>
       </c>
       <c r="B108" t="n">
-        <v>91889</v>
+        <v>101304</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657539</v>
+        <v>657545</v>
       </c>
       <c r="R108" t="n">
-        <v>6629301</v>
+        <v>6629427</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12420,7 +12420,7 @@
         <v>132400294</v>
       </c>
       <c r="B109" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132396621</v>
+        <v>132397898</v>
       </c>
       <c r="B111" t="n">
-        <v>5179</v>
+        <v>96534</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12660,32 +12660,35 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12693,10 +12696,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657605</v>
+        <v>657550</v>
       </c>
       <c r="R111" t="n">
-        <v>6629877</v>
+        <v>6629410</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12737,12 +12740,33 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12763,7 +12787,7 @@
         <v>132397047</v>
       </c>
       <c r="B112" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12889,60 +12913,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132397898</v>
+        <v>132393774</v>
       </c>
       <c r="B113" t="n">
-        <v>96531</v>
+        <v>91892</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657550</v>
+        <v>657579</v>
       </c>
       <c r="R113" t="n">
-        <v>6629410</v>
+        <v>6629235</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12969,103 +12981,96 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132393774</v>
+        <v>132396621</v>
       </c>
       <c r="B114" t="n">
-        <v>91889</v>
+        <v>5179</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657579</v>
+        <v>657605</v>
       </c>
       <c r="R114" t="n">
-        <v>6629235</v>
+        <v>6629877</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13092,21 +13097,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13115,16 +13110,21 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
         <v>132400286</v>
       </c>
       <c r="B115" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>132393771</v>
       </c>
       <c r="B116" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>132400290</v>
       </c>
       <c r="B117" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13467,48 +13467,57 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132393764</v>
+        <v>132397930</v>
       </c>
       <c r="B118" t="n">
-        <v>92349</v>
+        <v>4775</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>100299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657541</v>
+        <v>657534</v>
       </c>
       <c r="R118" t="n">
-        <v>6629301</v>
+        <v>6629364</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13535,87 +13544,107 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132393763</v>
+        <v>132397062</v>
       </c>
       <c r="B119" t="n">
-        <v>91889</v>
+        <v>96688</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657540</v>
+        <v>657621</v>
       </c>
       <c r="R119" t="n">
-        <v>6629314</v>
+        <v>6629728</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13642,49 +13671,45 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132393778</v>
+        <v>132393764</v>
       </c>
       <c r="B120" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13716,10 +13741,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657576</v>
+        <v>657541</v>
       </c>
       <c r="R120" t="n">
-        <v>6629236</v>
+        <v>6629301</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13751,7 +13776,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13761,7 +13786,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13788,38 +13813,37 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132397062</v>
+        <v>132397416</v>
       </c>
       <c r="B121" t="n">
-        <v>96685</v>
+        <v>91892</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13827,10 +13851,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657621</v>
+        <v>657575</v>
       </c>
       <c r="R121" t="n">
-        <v>6629728</v>
+        <v>6629496</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13877,7 +13901,27 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -13895,10 +13939,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132397416</v>
+        <v>132393763</v>
       </c>
       <c r="B122" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13924,22 +13968,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657575</v>
+        <v>657540</v>
       </c>
       <c r="R122" t="n">
-        <v>6629496</v>
+        <v>6629314</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13966,107 +14007,87 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132397917</v>
+        <v>132393778</v>
       </c>
       <c r="B123" t="n">
-        <v>97335</v>
+        <v>92352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>657557</v>
+        <v>657576</v>
       </c>
       <c r="R123" t="n">
-        <v>6629386</v>
+        <v>6629236</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14093,98 +14114,77 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397930</v>
+        <v>132397917</v>
       </c>
       <c r="B124" t="n">
-        <v>4775</v>
+        <v>97338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14192,10 +14192,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657534</v>
+        <v>657557</v>
       </c>
       <c r="R124" t="n">
-        <v>6629364</v>
+        <v>6629386</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14283,7 +14283,7 @@
         <v>132400291</v>
       </c>
       <c r="B125" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>132396661</v>
       </c>
       <c r="B127" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>132397021</v>
       </c>
       <c r="B128" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132393757</v>
+        <v>132396642</v>
       </c>
       <c r="B129" t="n">
-        <v>5179</v>
+        <v>92547</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14747,37 +14747,40 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>657623</v>
+        <v>657608</v>
       </c>
       <c r="R129" t="n">
-        <v>6629491</v>
+        <v>6629860</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14804,21 +14807,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14827,26 +14820,51 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132396642</v>
+        <v>132396986</v>
       </c>
       <c r="B130" t="n">
-        <v>92544</v>
+        <v>97658</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14854,26 +14872,27 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1339</v>
+        <v>2326</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14881,10 +14900,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657608</v>
+        <v>657604</v>
       </c>
       <c r="R130" t="n">
-        <v>6629860</v>
+        <v>6629772</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14930,27 +14949,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -14968,10 +14967,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132396986</v>
+        <v>132393757</v>
       </c>
       <c r="B131" t="n">
-        <v>97655</v>
+        <v>5179</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14979,41 +14978,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2326</v>
+        <v>100526</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657604</v>
+        <v>657623</v>
       </c>
       <c r="R131" t="n">
-        <v>6629772</v>
+        <v>6629491</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15040,11 +15035,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15053,21 +15058,16 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
         <v>132387913</v>
       </c>
       <c r="B132" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>132388723</v>
       </c>
       <c r="B133" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>132378501</v>
       </c>
       <c r="B134" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303827</v>
+        <v>132303809</v>
       </c>
       <c r="B29" t="n">
-        <v>91892</v>
+        <v>92615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657470</v>
+        <v>657556</v>
       </c>
       <c r="R29" t="n">
-        <v>6629072</v>
+        <v>6629205</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303818</v>
+        <v>132303827</v>
       </c>
       <c r="B30" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657503</v>
+        <v>657470</v>
       </c>
       <c r="R30" t="n">
-        <v>6629178</v>
+        <v>6629072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3793,32 +3793,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132303809</v>
+        <v>132303818</v>
       </c>
       <c r="B31" t="n">
-        <v>92615</v>
+        <v>92352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657556</v>
+        <v>657503</v>
       </c>
       <c r="R31" t="n">
-        <v>6629205</v>
+        <v>6629178</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132303822</v>
+        <v>132303789</v>
       </c>
       <c r="B36" t="n">
-        <v>97338</v>
+        <v>91912</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,23 +4344,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4368,10 +4364,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>657543</v>
+        <v>657601</v>
       </c>
       <c r="R36" t="n">
-        <v>6629113</v>
+        <v>6629846</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4403,7 +4399,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4413,7 +4409,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4440,10 +4436,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132303789</v>
+        <v>132303822</v>
       </c>
       <c r="B37" t="n">
-        <v>91912</v>
+        <v>97338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4451,19 +4447,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>657601</v>
+        <v>657543</v>
       </c>
       <c r="R37" t="n">
-        <v>6629846</v>
+        <v>6629113</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132303788</v>
+        <v>132303810</v>
       </c>
       <c r="B40" t="n">
-        <v>5179</v>
+        <v>101304</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657609</v>
+        <v>657560</v>
       </c>
       <c r="R40" t="n">
-        <v>6629874</v>
+        <v>6629165</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132303810</v>
+        <v>132303788</v>
       </c>
       <c r="B41" t="n">
-        <v>101304</v>
+        <v>5179</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657560</v>
+        <v>657609</v>
       </c>
       <c r="R41" t="n">
-        <v>6629165</v>
+        <v>6629874</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4971,32 +4971,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132303785</v>
+        <v>132303817</v>
       </c>
       <c r="B42" t="n">
-        <v>97338</v>
+        <v>92352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657626</v>
+        <v>657521</v>
       </c>
       <c r="R42" t="n">
-        <v>6629945</v>
+        <v>6629192</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5078,7 +5078,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132303817</v>
+        <v>132303833</v>
       </c>
       <c r="B43" t="n">
         <v>92352</v>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>657521</v>
+        <v>657443</v>
       </c>
       <c r="R43" t="n">
-        <v>6629192</v>
+        <v>6629220</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132303833</v>
+        <v>132303794</v>
       </c>
       <c r="B44" t="n">
-        <v>92352</v>
+        <v>57945</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657443</v>
+        <v>657621</v>
       </c>
       <c r="R44" t="n">
-        <v>6629220</v>
+        <v>6629620</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5265,7 +5265,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5292,10 +5297,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132303794</v>
+        <v>132303785</v>
       </c>
       <c r="B45" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5303,21 +5308,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5327,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657621</v>
+        <v>657626</v>
       </c>
       <c r="R45" t="n">
-        <v>6629620</v>
+        <v>6629945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5362,7 +5367,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5372,12 +5377,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303834</v>
+        <v>132303793</v>
       </c>
       <c r="B54" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,21 +6276,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657418</v>
+        <v>657601</v>
       </c>
       <c r="R54" t="n">
-        <v>6629221</v>
+        <v>6629629</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303793</v>
+        <v>132303834</v>
       </c>
       <c r="B55" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657601</v>
+        <v>657418</v>
       </c>
       <c r="R55" t="n">
-        <v>6629629</v>
+        <v>6629221</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,32 +6479,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132303791</v>
+        <v>132303797</v>
       </c>
       <c r="B56" t="n">
-        <v>4781</v>
+        <v>92117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102306</v>
+        <v>1106</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>657605</v>
+        <v>657663</v>
       </c>
       <c r="R56" t="n">
-        <v>6629850</v>
+        <v>6629597</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6586,32 +6586,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132303797</v>
+        <v>132303791</v>
       </c>
       <c r="B57" t="n">
-        <v>92117</v>
+        <v>4781</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1106</v>
+        <v>102306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657663</v>
+        <v>657605</v>
       </c>
       <c r="R57" t="n">
-        <v>6629597</v>
+        <v>6629850</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7010,10 +7010,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132303828</v>
+        <v>132303805</v>
       </c>
       <c r="B61" t="n">
-        <v>91892</v>
+        <v>97338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>657472</v>
+        <v>657549</v>
       </c>
       <c r="R61" t="n">
-        <v>6629096</v>
+        <v>6629245</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7448,10 +7448,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303805</v>
+        <v>132303828</v>
       </c>
       <c r="B65" t="n">
-        <v>97338</v>
+        <v>91892</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>657549</v>
+        <v>657472</v>
       </c>
       <c r="R65" t="n">
-        <v>6629245</v>
+        <v>6629096</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9338,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393780</v>
+        <v>132393768</v>
       </c>
       <c r="B82" t="n">
-        <v>91912</v>
+        <v>91892</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9349,19 +9349,23 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9369,10 +9373,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657500</v>
+        <v>657498</v>
       </c>
       <c r="R82" t="n">
-        <v>6629450</v>
+        <v>6629248</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9404,7 +9408,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9414,7 +9418,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9441,10 +9445,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132393768</v>
+        <v>132393780</v>
       </c>
       <c r="B83" t="n">
-        <v>91892</v>
+        <v>91912</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9452,23 +9456,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657498</v>
+        <v>657500</v>
       </c>
       <c r="R83" t="n">
-        <v>6629248</v>
+        <v>6629450</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9670,10 +9670,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132397799</v>
+        <v>132393770</v>
       </c>
       <c r="B85" t="n">
-        <v>92547</v>
+        <v>8444</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,40 +9681,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657535</v>
+        <v>657487</v>
       </c>
       <c r="R85" t="n">
-        <v>6629432</v>
+        <v>6629134</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9741,65 +9738,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132393770</v>
+        <v>132398283</v>
       </c>
       <c r="B86" t="n">
-        <v>8444</v>
+        <v>106222</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9807,37 +9788,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657487</v>
+        <v>657575</v>
       </c>
       <c r="R86" t="n">
-        <v>6629134</v>
+        <v>6629279</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9864,49 +9849,40 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132398283</v>
+        <v>132397799</v>
       </c>
       <c r="B87" t="n">
-        <v>106222</v>
+        <v>92547</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9914,27 +9890,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9942,10 +9917,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657575</v>
+        <v>657535</v>
       </c>
       <c r="R87" t="n">
-        <v>6629279</v>
+        <v>6629432</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9989,6 +9964,31 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10566,10 +10566,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132397298</v>
+        <v>132398032</v>
       </c>
       <c r="B93" t="n">
-        <v>92316</v>
+        <v>8444</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10577,26 +10577,32 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4217</v>
+        <v>106554</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10604,10 +10610,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657657</v>
+        <v>657485</v>
       </c>
       <c r="R93" t="n">
-        <v>6629610</v>
+        <v>6629132</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10654,27 +10660,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10692,32 +10698,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132397367</v>
+        <v>132397298</v>
       </c>
       <c r="B94" t="n">
-        <v>91814</v>
+        <v>92316</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3242</v>
+        <v>4217</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10730,10 +10736,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657627</v>
+        <v>657657</v>
       </c>
       <c r="R94" t="n">
-        <v>6629577</v>
+        <v>6629610</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10795,12 +10801,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10818,43 +10824,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132398032</v>
+        <v>132397367</v>
       </c>
       <c r="B95" t="n">
-        <v>8444</v>
+        <v>91814</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106554</v>
+        <v>3242</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657485</v>
+        <v>657627</v>
       </c>
       <c r="R95" t="n">
-        <v>6629132</v>
+        <v>6629577</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10912,27 +10912,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10950,48 +10950,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132393773</v>
+        <v>132398021</v>
       </c>
       <c r="B96" t="n">
-        <v>91892</v>
+        <v>8455</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657548</v>
+        <v>657497</v>
       </c>
       <c r="R96" t="n">
-        <v>6629166</v>
+        <v>6629177</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11018,39 +11027,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11280,57 +11305,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132398021</v>
+        <v>132393773</v>
       </c>
       <c r="B99" t="n">
-        <v>8455</v>
+        <v>91892</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657497</v>
+        <v>657548</v>
       </c>
       <c r="R99" t="n">
-        <v>6629177</v>
+        <v>6629166</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11357,55 +11373,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132397898</v>
+        <v>132396621</v>
       </c>
       <c r="B111" t="n">
-        <v>96534</v>
+        <v>5179</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12660,35 +12660,32 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12696,10 +12693,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657550</v>
+        <v>657605</v>
       </c>
       <c r="R111" t="n">
-        <v>6629410</v>
+        <v>6629877</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12740,33 +12737,12 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12784,45 +12760,46 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132397047</v>
+        <v>132397898</v>
       </c>
       <c r="B112" t="n">
-        <v>91316</v>
+        <v>96534</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2008</v>
+        <v>210</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12830,10 +12807,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657618</v>
+        <v>657550</v>
       </c>
       <c r="R112" t="n">
-        <v>6629739</v>
+        <v>6629410</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12880,7 +12857,7 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -12893,9 +12870,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -12913,10 +12895,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132393774</v>
+        <v>132397047</v>
       </c>
       <c r="B113" t="n">
-        <v>91892</v>
+        <v>91316</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12924,37 +12906,48 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>2008</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657579</v>
+        <v>657618</v>
       </c>
       <c r="R113" t="n">
-        <v>6629235</v>
+        <v>6629739</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12981,96 +12974,98 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132396621</v>
+        <v>132393774</v>
       </c>
       <c r="B114" t="n">
-        <v>5179</v>
+        <v>91892</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657605</v>
+        <v>657579</v>
       </c>
       <c r="R114" t="n">
-        <v>6629877</v>
+        <v>6629235</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13097,11 +13092,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13110,21 +13115,16 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13467,10 +13467,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132397930</v>
+        <v>132397062</v>
       </c>
       <c r="B118" t="n">
-        <v>4775</v>
+        <v>96688</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13478,32 +13478,27 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13511,10 +13506,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657534</v>
+        <v>657621</v>
       </c>
       <c r="R118" t="n">
-        <v>6629364</v>
+        <v>6629728</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13561,27 +13556,7 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13599,52 +13574,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132397062</v>
+        <v>132393764</v>
       </c>
       <c r="B119" t="n">
-        <v>96688</v>
+        <v>92352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657621</v>
+        <v>657541</v>
       </c>
       <c r="R119" t="n">
-        <v>6629728</v>
+        <v>6629301</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13671,83 +13642,90 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132393764</v>
+        <v>132397416</v>
       </c>
       <c r="B120" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657541</v>
+        <v>657575</v>
       </c>
       <c r="R120" t="n">
-        <v>6629301</v>
+        <v>6629496</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13774,46 +13752,62 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132397416</v>
+        <v>132393763</v>
       </c>
       <c r="B121" t="n">
         <v>91892</v>
@@ -13842,22 +13836,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657575</v>
+        <v>657540</v>
       </c>
       <c r="R121" t="n">
-        <v>6629496</v>
+        <v>6629314</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13884,87 +13875,71 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132393763</v>
+        <v>132393778</v>
       </c>
       <c r="B122" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13974,10 +13949,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657540</v>
+        <v>657576</v>
       </c>
       <c r="R122" t="n">
-        <v>6629314</v>
+        <v>6629236</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14009,7 +13984,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14019,7 +13994,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14046,48 +14021,52 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132393778</v>
+        <v>132397917</v>
       </c>
       <c r="B123" t="n">
-        <v>92352</v>
+        <v>97338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>657576</v>
+        <v>657557</v>
       </c>
       <c r="R123" t="n">
-        <v>6629236</v>
+        <v>6629386</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14114,77 +14093,98 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397917</v>
+        <v>132397930</v>
       </c>
       <c r="B124" t="n">
-        <v>97338</v>
+        <v>4775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14192,10 +14192,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657557</v>
+        <v>657534</v>
       </c>
       <c r="R124" t="n">
-        <v>6629386</v>
+        <v>6629364</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14280,48 +14280,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132400291</v>
+        <v>132400284</v>
       </c>
       <c r="B125" t="n">
-        <v>91892</v>
+        <v>8444</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657534</v>
+        <v>657490</v>
       </c>
       <c r="R125" t="n">
-        <v>6629757</v>
+        <v>6629140</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14353,7 +14350,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14363,12 +14360,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14396,10 +14388,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132400284</v>
+        <v>132396661</v>
       </c>
       <c r="B126" t="n">
-        <v>8444</v>
+        <v>96438</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14407,34 +14399,38 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>657490</v>
+        <v>657626</v>
       </c>
       <c r="R126" t="n">
-        <v>6629140</v>
+        <v>6629856</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14464,50 +14460,44 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132396661</v>
+        <v>132397021</v>
       </c>
       <c r="B127" t="n">
-        <v>96438</v>
+        <v>92615</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14515,27 +14505,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2818</v>
+        <v>3298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14543,10 +14532,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>657626</v>
+        <v>657607</v>
       </c>
       <c r="R127" t="n">
-        <v>6629856</v>
+        <v>6629730</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14587,12 +14576,33 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14610,32 +14620,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132397021</v>
+        <v>132400291</v>
       </c>
       <c r="B128" t="n">
-        <v>92615</v>
+        <v>91892</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14644,14 +14654,14 @@
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>657607</v>
+        <v>657534</v>
       </c>
       <c r="R128" t="n">
-        <v>6629730</v>
+        <v>6629757</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14681,9 +14691,24 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14696,40 +14721,15 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132229113</v>
+        <v>132229131</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657681</v>
+        <v>657670</v>
       </c>
       <c r="R17" t="n">
-        <v>6629873</v>
+        <v>6629756</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132229131</v>
+        <v>132229113</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657670</v>
+        <v>657681</v>
       </c>
       <c r="R18" t="n">
-        <v>6629756</v>
+        <v>6629873</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4543,32 +4543,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132303815</v>
+        <v>132303821</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>97338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>657525</v>
+        <v>657531</v>
       </c>
       <c r="R38" t="n">
-        <v>6629176</v>
+        <v>6629123</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4650,32 +4650,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132303821</v>
+        <v>132303815</v>
       </c>
       <c r="B39" t="n">
-        <v>97338</v>
+        <v>92352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>657531</v>
+        <v>657525</v>
       </c>
       <c r="R39" t="n">
-        <v>6629123</v>
+        <v>6629176</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -8897,48 +8897,52 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132393767</v>
+        <v>132395803</v>
       </c>
       <c r="B78" t="n">
-        <v>97338</v>
+        <v>97658</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657539</v>
+        <v>657653</v>
       </c>
       <c r="R78" t="n">
-        <v>6629272</v>
+        <v>6629952</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8965,21 +8969,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8988,68 +8982,69 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132395803</v>
+        <v>132393767</v>
       </c>
       <c r="B79" t="n">
-        <v>97658</v>
+        <v>97338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657653</v>
+        <v>657539</v>
       </c>
       <c r="R79" t="n">
-        <v>6629952</v>
+        <v>6629272</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9076,11 +9071,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9089,21 +9094,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9338,48 +9338,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393768</v>
+        <v>132396889</v>
       </c>
       <c r="B82" t="n">
-        <v>91892</v>
+        <v>4781</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657498</v>
+        <v>657576</v>
       </c>
       <c r="R82" t="n">
-        <v>6629248</v>
+        <v>6629830</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9406,21 +9411,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9429,16 +9424,36 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9548,53 +9563,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132396889</v>
+        <v>132393768</v>
       </c>
       <c r="B84" t="n">
-        <v>4781</v>
+        <v>91892</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>657576</v>
+        <v>657498</v>
       </c>
       <c r="R84" t="n">
-        <v>6629830</v>
+        <v>6629248</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9621,11 +9631,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9634,46 +9654,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132393770</v>
+        <v>132397799</v>
       </c>
       <c r="B85" t="n">
-        <v>8444</v>
+        <v>92547</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,37 +9681,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657487</v>
+        <v>657535</v>
       </c>
       <c r="R85" t="n">
-        <v>6629134</v>
+        <v>6629432</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9738,49 +9741,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132398283</v>
+        <v>132393770</v>
       </c>
       <c r="B86" t="n">
-        <v>106222</v>
+        <v>8444</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9788,41 +9807,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657575</v>
+        <v>657487</v>
       </c>
       <c r="R86" t="n">
-        <v>6629279</v>
+        <v>6629134</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9849,40 +9864,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B87" t="n">
-        <v>92547</v>
+        <v>106222</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9890,26 +9914,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9917,10 +9942,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R87" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9964,31 +9989,6 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11873,7 +11873,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132400288</v>
+        <v>132393753</v>
       </c>
       <c r="B104" t="n">
         <v>92352</v>
@@ -11902,22 +11902,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657615</v>
+        <v>657605</v>
       </c>
       <c r="R104" t="n">
-        <v>6629610</v>
+        <v>6629627</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11959,37 +11956,31 @@
           <t>12:26</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132393753</v>
+        <v>132400288</v>
       </c>
       <c r="B105" t="n">
         <v>92352</v>
@@ -12018,19 +12009,22 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657605</v>
+        <v>657615</v>
       </c>
       <c r="R105" t="n">
-        <v>6629627</v>
+        <v>6629610</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12072,24 +12066,30 @@
           <t>12:26</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -13467,10 +13467,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132397062</v>
+        <v>132397930</v>
       </c>
       <c r="B118" t="n">
-        <v>96688</v>
+        <v>4775</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13478,27 +13478,32 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13506,10 +13511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657621</v>
+        <v>657534</v>
       </c>
       <c r="R118" t="n">
-        <v>6629728</v>
+        <v>6629364</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13556,7 +13561,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13574,48 +13599,52 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132393764</v>
+        <v>132397062</v>
       </c>
       <c r="B119" t="n">
-        <v>92352</v>
+        <v>96688</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657541</v>
+        <v>657621</v>
       </c>
       <c r="R119" t="n">
-        <v>6629301</v>
+        <v>6629728</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13642,90 +13671,83 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132397416</v>
+        <v>132393764</v>
       </c>
       <c r="B120" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657575</v>
+        <v>657541</v>
       </c>
       <c r="R120" t="n">
-        <v>6629496</v>
+        <v>6629301</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13752,62 +13774,46 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132393763</v>
+        <v>132397416</v>
       </c>
       <c r="B121" t="n">
         <v>91892</v>
@@ -13836,19 +13842,22 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657540</v>
+        <v>657575</v>
       </c>
       <c r="R121" t="n">
-        <v>6629314</v>
+        <v>6629496</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13875,71 +13884,87 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132393778</v>
+        <v>132393763</v>
       </c>
       <c r="B122" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13949,10 +13974,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657576</v>
+        <v>657540</v>
       </c>
       <c r="R122" t="n">
-        <v>6629236</v>
+        <v>6629314</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13984,7 +14009,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13994,7 +14019,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14021,52 +14046,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132397917</v>
+        <v>132393778</v>
       </c>
       <c r="B123" t="n">
-        <v>97338</v>
+        <v>92352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>657557</v>
+        <v>657576</v>
       </c>
       <c r="R123" t="n">
-        <v>6629386</v>
+        <v>6629236</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14093,98 +14114,77 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397930</v>
+        <v>132397917</v>
       </c>
       <c r="B124" t="n">
-        <v>4775</v>
+        <v>97338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14192,10 +14192,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657534</v>
+        <v>657557</v>
       </c>
       <c r="R124" t="n">
-        <v>6629364</v>
+        <v>6629386</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303809</v>
+        <v>132303827</v>
       </c>
       <c r="B29" t="n">
-        <v>92615</v>
+        <v>91892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657556</v>
+        <v>657470</v>
       </c>
       <c r="R29" t="n">
-        <v>6629205</v>
+        <v>6629072</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303827</v>
+        <v>132303809</v>
       </c>
       <c r="B30" t="n">
-        <v>91892</v>
+        <v>92615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657470</v>
+        <v>657556</v>
       </c>
       <c r="R30" t="n">
-        <v>6629072</v>
+        <v>6629205</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132303811</v>
+        <v>132303836</v>
       </c>
       <c r="B32" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>657543</v>
+        <v>657418</v>
       </c>
       <c r="R32" t="n">
-        <v>6629159</v>
+        <v>6629375</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132303836</v>
+        <v>132303811</v>
       </c>
       <c r="B33" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>657418</v>
+        <v>657543</v>
       </c>
       <c r="R33" t="n">
-        <v>6629375</v>
+        <v>6629159</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132303789</v>
+        <v>132303822</v>
       </c>
       <c r="B36" t="n">
-        <v>91912</v>
+        <v>97338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,19 +4344,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4364,10 +4368,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>657601</v>
+        <v>657543</v>
       </c>
       <c r="R36" t="n">
-        <v>6629846</v>
+        <v>6629113</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4399,7 +4403,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4409,7 +4413,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4436,10 +4440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132303822</v>
+        <v>132303789</v>
       </c>
       <c r="B37" t="n">
-        <v>97338</v>
+        <v>91912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,23 +4451,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>657543</v>
+        <v>657601</v>
       </c>
       <c r="R37" t="n">
-        <v>6629113</v>
+        <v>6629846</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132303794</v>
+        <v>132303785</v>
       </c>
       <c r="B44" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657621</v>
+        <v>657626</v>
       </c>
       <c r="R44" t="n">
-        <v>6629620</v>
+        <v>6629945</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5265,12 +5265,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5297,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132303785</v>
+        <v>132303794</v>
       </c>
       <c r="B45" t="n">
-        <v>97338</v>
+        <v>57945</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5308,21 +5303,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5327,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657626</v>
+        <v>657621</v>
       </c>
       <c r="R45" t="n">
-        <v>6629945</v>
+        <v>6629620</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5377,7 +5372,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5730,32 +5730,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132303804</v>
+        <v>132303819</v>
       </c>
       <c r="B49" t="n">
-        <v>97338</v>
+        <v>91855</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>657546</v>
+        <v>657531</v>
       </c>
       <c r="R49" t="n">
-        <v>6629244</v>
+        <v>6629126</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,32 +5837,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132303819</v>
+        <v>132303804</v>
       </c>
       <c r="B50" t="n">
-        <v>91855</v>
+        <v>97338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>657531</v>
+        <v>657546</v>
       </c>
       <c r="R50" t="n">
-        <v>6629126</v>
+        <v>6629244</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5944,32 +5944,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303813</v>
+        <v>132303816</v>
       </c>
       <c r="B51" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657528</v>
+        <v>657523</v>
       </c>
       <c r="R51" t="n">
-        <v>6629154</v>
+        <v>6629179</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303816</v>
+        <v>132303823</v>
       </c>
       <c r="B52" t="n">
-        <v>92352</v>
+        <v>97338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657523</v>
+        <v>657524</v>
       </c>
       <c r="R52" t="n">
-        <v>6629179</v>
+        <v>6629112</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303823</v>
+        <v>132303793</v>
       </c>
       <c r="B53" t="n">
-        <v>97338</v>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657524</v>
+        <v>657601</v>
       </c>
       <c r="R53" t="n">
-        <v>6629112</v>
+        <v>6629629</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303793</v>
+        <v>132303813</v>
       </c>
       <c r="B54" t="n">
-        <v>5199</v>
+        <v>91892</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657601</v>
+        <v>657528</v>
       </c>
       <c r="R54" t="n">
-        <v>6629629</v>
+        <v>6629154</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7010,10 +7010,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132303805</v>
+        <v>132303828</v>
       </c>
       <c r="B61" t="n">
-        <v>97338</v>
+        <v>91892</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>657549</v>
+        <v>657472</v>
       </c>
       <c r="R61" t="n">
-        <v>6629245</v>
+        <v>6629096</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7117,10 +7117,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132303802</v>
+        <v>132303805</v>
       </c>
       <c r="B62" t="n">
-        <v>57945</v>
+        <v>97338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,21 +7128,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>657568</v>
+        <v>657549</v>
       </c>
       <c r="R62" t="n">
-        <v>6629349</v>
+        <v>6629245</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7197,12 +7197,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7341,32 +7336,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132303792</v>
+        <v>132303802</v>
       </c>
       <c r="B64" t="n">
-        <v>4781</v>
+        <v>57945</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7376,10 +7371,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>657607</v>
+        <v>657568</v>
       </c>
       <c r="R64" t="n">
-        <v>6629839</v>
+        <v>6629349</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7411,7 +7406,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7421,7 +7416,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,32 +7448,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303828</v>
+        <v>132303792</v>
       </c>
       <c r="B65" t="n">
-        <v>91892</v>
+        <v>4781</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>657472</v>
+        <v>657607</v>
       </c>
       <c r="R65" t="n">
-        <v>6629096</v>
+        <v>6629839</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8445,10 +8445,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132395560</v>
+        <v>132393747</v>
       </c>
       <c r="B74" t="n">
-        <v>96438</v>
+        <v>91855</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8456,41 +8456,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657653</v>
+        <v>657641</v>
       </c>
       <c r="R74" t="n">
-        <v>6629952</v>
+        <v>6629957</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8517,55 +8513,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132393747</v>
+        <v>132395560</v>
       </c>
       <c r="B75" t="n">
-        <v>91855</v>
+        <v>96438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8573,37 +8563,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657641</v>
+        <v>657653</v>
       </c>
       <c r="R75" t="n">
-        <v>6629957</v>
+        <v>6629952</v>
       </c>
       <c r="S75" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8630,39 +8624,45 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8897,52 +8897,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132395803</v>
+        <v>132393767</v>
       </c>
       <c r="B78" t="n">
-        <v>97658</v>
+        <v>97338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657653</v>
+        <v>657539</v>
       </c>
       <c r="R78" t="n">
-        <v>6629952</v>
+        <v>6629272</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8969,11 +8965,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8982,69 +8988,68 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132393767</v>
+        <v>132395803</v>
       </c>
       <c r="B79" t="n">
-        <v>97338</v>
+        <v>97658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657539</v>
+        <v>657653</v>
       </c>
       <c r="R79" t="n">
-        <v>6629272</v>
+        <v>6629952</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9071,21 +9076,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9094,16 +9089,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9338,53 +9338,44 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132396889</v>
+        <v>132393780</v>
       </c>
       <c r="B82" t="n">
-        <v>4781</v>
+        <v>91912</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102306</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657576</v>
+        <v>657500</v>
       </c>
       <c r="R82" t="n">
-        <v>6629830</v>
+        <v>6629450</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9411,11 +9402,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9424,80 +9425,69 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132393780</v>
+        <v>132396889</v>
       </c>
       <c r="B83" t="n">
-        <v>91912</v>
+        <v>4781</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>102306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657500</v>
+        <v>657576</v>
       </c>
       <c r="R83" t="n">
-        <v>6629450</v>
+        <v>6629830</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9524,21 +9514,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9547,16 +9527,36 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10005,53 +10005,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132398041</v>
+        <v>132393758</v>
       </c>
       <c r="B88" t="n">
-        <v>9414</v>
+        <v>91892</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>105076</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657485</v>
+        <v>657570</v>
       </c>
       <c r="R88" t="n">
-        <v>6629132</v>
+        <v>6629495</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10078,87 +10073,71 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132393760</v>
+        <v>132393762</v>
       </c>
       <c r="B89" t="n">
-        <v>101304</v>
+        <v>97338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10168,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657538</v>
+        <v>657575</v>
       </c>
       <c r="R89" t="n">
-        <v>6629429</v>
+        <v>6629363</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10203,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10213,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10240,32 +10219,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132393758</v>
+        <v>132393760</v>
       </c>
       <c r="B90" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10275,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657570</v>
+        <v>657538</v>
       </c>
       <c r="R90" t="n">
-        <v>6629495</v>
+        <v>6629429</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10310,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10320,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10347,10 +10326,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132400287</v>
+        <v>132398041</v>
       </c>
       <c r="B91" t="n">
-        <v>101304</v>
+        <v>9414</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10358,38 +10337,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>105076</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657564</v>
+        <v>657485</v>
       </c>
       <c r="R91" t="n">
-        <v>6629426</v>
+        <v>6629132</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10419,19 +10399,9 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10444,63 +10414,92 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+        </is>
+      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132393762</v>
+        <v>132400287</v>
       </c>
       <c r="B92" t="n">
-        <v>97338</v>
+        <v>101304</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>657575</v>
+        <v>657564</v>
       </c>
       <c r="R92" t="n">
-        <v>6629363</v>
+        <v>6629426</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10529,7 +10528,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10539,7 +10538,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10548,61 +10547,56 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132398032</v>
+        <v>132397367</v>
       </c>
       <c r="B93" t="n">
-        <v>8444</v>
+        <v>91814</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106554</v>
+        <v>3242</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10610,10 +10604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657485</v>
+        <v>657627</v>
       </c>
       <c r="R93" t="n">
-        <v>6629132</v>
+        <v>6629577</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10660,27 +10654,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10698,10 +10692,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132397298</v>
+        <v>132398032</v>
       </c>
       <c r="B94" t="n">
-        <v>92316</v>
+        <v>8444</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10709,26 +10703,32 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4217</v>
+        <v>106554</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657657</v>
+        <v>657485</v>
       </c>
       <c r="R94" t="n">
-        <v>6629610</v>
+        <v>6629132</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10786,27 +10786,27 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10824,32 +10824,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132397367</v>
+        <v>132397298</v>
       </c>
       <c r="B95" t="n">
-        <v>91814</v>
+        <v>92316</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3242</v>
+        <v>4217</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657627</v>
+        <v>657657</v>
       </c>
       <c r="R95" t="n">
-        <v>6629577</v>
+        <v>6629610</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10927,12 +10927,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10950,57 +10950,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132398021</v>
+        <v>132393773</v>
       </c>
       <c r="B96" t="n">
-        <v>8455</v>
+        <v>91892</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657497</v>
+        <v>657548</v>
       </c>
       <c r="R96" t="n">
-        <v>6629177</v>
+        <v>6629166</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11027,55 +11018,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11305,32 +11280,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132393773</v>
+        <v>132393772</v>
       </c>
       <c r="B99" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11340,10 +11315,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657548</v>
+        <v>657497</v>
       </c>
       <c r="R99" t="n">
-        <v>6629166</v>
+        <v>6629103</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11375,7 +11350,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11385,7 +11360,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11412,10 +11387,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132393772</v>
+        <v>132398021</v>
       </c>
       <c r="B100" t="n">
-        <v>101304</v>
+        <v>8455</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11423,24 +11398,33 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
@@ -11450,10 +11434,10 @@
         <v>657497</v>
       </c>
       <c r="R100" t="n">
-        <v>6629103</v>
+        <v>6629177</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11480,39 +11464,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11644,10 +11644,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B102" t="n">
-        <v>4775</v>
+        <v>101304</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,42 +11655,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R102" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11717,11 +11712,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11730,46 +11735,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132393776</v>
+        <v>132396920</v>
       </c>
       <c r="B103" t="n">
-        <v>101304</v>
+        <v>4775</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11777,37 +11762,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657575</v>
+        <v>657583</v>
       </c>
       <c r="R103" t="n">
-        <v>6629232</v>
+        <v>6629810</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11834,21 +11824,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11857,16 +11837,36 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12096,32 +12096,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393751</v>
+        <v>132393761</v>
       </c>
       <c r="B106" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657577</v>
+        <v>657545</v>
       </c>
       <c r="R106" t="n">
-        <v>6629624</v>
+        <v>6629427</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393761</v>
+        <v>132393751</v>
       </c>
       <c r="B108" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657545</v>
+        <v>657577</v>
       </c>
       <c r="R108" t="n">
-        <v>6629427</v>
+        <v>6629624</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12417,10 +12417,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132400294</v>
+        <v>132393750</v>
       </c>
       <c r="B109" t="n">
-        <v>91912</v>
+        <v>57945</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,44 +12428,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>657599</v>
+        <v>657622</v>
       </c>
       <c r="R109" t="n">
-        <v>6629841</v>
+        <v>6629865</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12494,7 +12487,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12504,12 +12497,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12518,29 +12511,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132393750</v>
+        <v>132400294</v>
       </c>
       <c r="B110" t="n">
-        <v>57945</v>
+        <v>91912</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12548,37 +12540,44 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>657622</v>
+        <v>657599</v>
       </c>
       <c r="R110" t="n">
-        <v>6629865</v>
+        <v>6629841</v>
       </c>
       <c r="S110" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12607,7 +12606,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12617,12 +12616,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12631,61 +12630,64 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132396621</v>
+        <v>132397047</v>
       </c>
       <c r="B111" t="n">
-        <v>5179</v>
+        <v>91316</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12693,10 +12695,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657605</v>
+        <v>657618</v>
       </c>
       <c r="R111" t="n">
-        <v>6629877</v>
+        <v>6629739</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12737,12 +12739,28 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12895,10 +12913,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132397047</v>
+        <v>132393774</v>
       </c>
       <c r="B113" t="n">
-        <v>91316</v>
+        <v>91892</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12906,48 +12924,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2008</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657618</v>
+        <v>657579</v>
       </c>
       <c r="R113" t="n">
-        <v>6629739</v>
+        <v>6629235</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12974,98 +12981,96 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132393774</v>
+        <v>132396621</v>
       </c>
       <c r="B114" t="n">
-        <v>91892</v>
+        <v>5179</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657579</v>
+        <v>657605</v>
       </c>
       <c r="R114" t="n">
-        <v>6629235</v>
+        <v>6629877</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13092,21 +13097,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13115,16 +13110,21 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13599,32 +13599,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132397062</v>
+        <v>132397917</v>
       </c>
       <c r="B119" t="n">
-        <v>96688</v>
+        <v>97338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13638,10 +13638,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657621</v>
+        <v>657557</v>
       </c>
       <c r="R119" t="n">
-        <v>6629728</v>
+        <v>6629386</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13688,7 +13688,27 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13706,32 +13726,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132393764</v>
+        <v>132393763</v>
       </c>
       <c r="B120" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13741,10 +13761,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657541</v>
+        <v>657540</v>
       </c>
       <c r="R120" t="n">
-        <v>6629301</v>
+        <v>6629314</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13776,7 +13796,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13786,7 +13806,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13939,32 +13959,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132393763</v>
+        <v>132393764</v>
       </c>
       <c r="B122" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13974,10 +13994,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657540</v>
+        <v>657541</v>
       </c>
       <c r="R122" t="n">
-        <v>6629314</v>
+        <v>6629301</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14009,7 +14029,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14019,7 +14039,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14153,32 +14173,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397917</v>
+        <v>132397062</v>
       </c>
       <c r="B124" t="n">
-        <v>97338</v>
+        <v>96688</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14192,10 +14212,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657557</v>
+        <v>657621</v>
       </c>
       <c r="R124" t="n">
-        <v>6629386</v>
+        <v>6629728</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14242,27 +14262,7 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14736,10 +14736,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132396642</v>
+        <v>132396986</v>
       </c>
       <c r="B129" t="n">
-        <v>92547</v>
+        <v>97658</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14747,26 +14747,27 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1339</v>
+        <v>2326</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14774,10 +14775,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>657608</v>
+        <v>657604</v>
       </c>
       <c r="R129" t="n">
-        <v>6629860</v>
+        <v>6629772</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14823,27 +14824,7 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14861,10 +14842,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132396986</v>
+        <v>132396642</v>
       </c>
       <c r="B130" t="n">
-        <v>97658</v>
+        <v>92547</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14872,27 +14853,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2326</v>
+        <v>1339</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14900,10 +14880,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657604</v>
+        <v>657608</v>
       </c>
       <c r="R130" t="n">
-        <v>6629772</v>
+        <v>6629860</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14949,7 +14929,27 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132229129</v>
+        <v>132229117</v>
       </c>
       <c r="B12" t="n">
-        <v>92615</v>
+        <v>97338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657617</v>
+        <v>657592</v>
       </c>
       <c r="R12" t="n">
-        <v>6629722</v>
+        <v>6629803</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132229117</v>
+        <v>132229129</v>
       </c>
       <c r="B13" t="n">
-        <v>97338</v>
+        <v>92615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657592</v>
+        <v>657617</v>
       </c>
       <c r="R13" t="n">
-        <v>6629803</v>
+        <v>6629722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3151,32 +3151,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132229105</v>
+        <v>132229135</v>
       </c>
       <c r="B25" t="n">
-        <v>97338</v>
+        <v>4781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>657629</v>
+        <v>657669</v>
       </c>
       <c r="R25" t="n">
-        <v>6629952</v>
+        <v>6629815</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,32 +3258,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132229135</v>
+        <v>132229105</v>
       </c>
       <c r="B26" t="n">
-        <v>4781</v>
+        <v>97338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>657669</v>
+        <v>657629</v>
       </c>
       <c r="R26" t="n">
-        <v>6629815</v>
+        <v>6629952</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132303810</v>
+        <v>132303788</v>
       </c>
       <c r="B40" t="n">
-        <v>101304</v>
+        <v>5179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4768,21 +4768,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657560</v>
+        <v>657609</v>
       </c>
       <c r="R40" t="n">
-        <v>6629165</v>
+        <v>6629874</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132303788</v>
+        <v>132303810</v>
       </c>
       <c r="B41" t="n">
-        <v>5179</v>
+        <v>101304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657609</v>
+        <v>657560</v>
       </c>
       <c r="R41" t="n">
-        <v>6629874</v>
+        <v>6629165</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5944,32 +5944,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303816</v>
+        <v>132303813</v>
       </c>
       <c r="B51" t="n">
-        <v>92352</v>
+        <v>91892</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657523</v>
+        <v>657528</v>
       </c>
       <c r="R51" t="n">
-        <v>6629179</v>
+        <v>6629154</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303823</v>
+        <v>132303816</v>
       </c>
       <c r="B52" t="n">
-        <v>97338</v>
+        <v>92352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657524</v>
+        <v>657523</v>
       </c>
       <c r="R52" t="n">
-        <v>6629112</v>
+        <v>6629179</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303793</v>
+        <v>132303823</v>
       </c>
       <c r="B53" t="n">
-        <v>5199</v>
+        <v>97338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657601</v>
+        <v>657524</v>
       </c>
       <c r="R53" t="n">
-        <v>6629629</v>
+        <v>6629112</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303813</v>
+        <v>132303834</v>
       </c>
       <c r="B54" t="n">
-        <v>91892</v>
+        <v>4781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657528</v>
+        <v>657418</v>
       </c>
       <c r="R54" t="n">
-        <v>6629154</v>
+        <v>6629221</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303834</v>
+        <v>132303793</v>
       </c>
       <c r="B55" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657418</v>
+        <v>657601</v>
       </c>
       <c r="R55" t="n">
-        <v>6629221</v>
+        <v>6629629</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7224,7 +7224,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303801</v>
+        <v>132303802</v>
       </c>
       <c r="B63" t="n">
         <v>57945</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>657607</v>
+        <v>657568</v>
       </c>
       <c r="R63" t="n">
-        <v>6629402</v>
+        <v>6629349</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7336,7 +7336,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132303802</v>
+        <v>132303801</v>
       </c>
       <c r="B64" t="n">
         <v>57945</v>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>657568</v>
+        <v>657607</v>
       </c>
       <c r="R64" t="n">
-        <v>6629349</v>
+        <v>6629402</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8897,48 +8897,51 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132393767</v>
+        <v>132398009</v>
       </c>
       <c r="B78" t="n">
-        <v>97338</v>
+        <v>91855</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657539</v>
+        <v>657441</v>
       </c>
       <c r="R78" t="n">
-        <v>6629272</v>
+        <v>6629193</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8965,91 +8968,98 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132395803</v>
+        <v>132393767</v>
       </c>
       <c r="B79" t="n">
-        <v>97658</v>
+        <v>97338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657653</v>
+        <v>657539</v>
       </c>
       <c r="R79" t="n">
-        <v>6629952</v>
+        <v>6629272</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9076,11 +9086,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9089,31 +9109,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132398009</v>
+        <v>132395803</v>
       </c>
       <c r="B80" t="n">
-        <v>91855</v>
+        <v>97658</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9121,26 +9136,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>2326</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9148,10 +9164,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657441</v>
+        <v>657653</v>
       </c>
       <c r="R80" t="n">
-        <v>6629193</v>
+        <v>6629952</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9192,28 +9208,12 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10950,32 +10950,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132393773</v>
+        <v>132393772</v>
       </c>
       <c r="B96" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657548</v>
+        <v>657497</v>
       </c>
       <c r="R96" t="n">
-        <v>6629166</v>
+        <v>6629103</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11057,7 +11057,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132400285</v>
+        <v>132393773</v>
       </c>
       <c r="B97" t="n">
         <v>91892</v>
@@ -11086,22 +11086,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657528</v>
+        <v>657548</v>
       </c>
       <c r="R97" t="n">
-        <v>6629248</v>
+        <v>6629166</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11130,7 +11127,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11140,12 +11137,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11154,64 +11146,66 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132400283</v>
+        <v>132400285</v>
       </c>
       <c r="B98" t="n">
-        <v>96534</v>
+        <v>91892</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657491</v>
+        <v>657528</v>
       </c>
       <c r="R98" t="n">
-        <v>6629142</v>
+        <v>6629248</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11243,7 +11237,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11253,7 +11247,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11262,6 +11261,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11280,10 +11280,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132393772</v>
+        <v>132400283</v>
       </c>
       <c r="B99" t="n">
-        <v>101304</v>
+        <v>96534</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11291,37 +11291,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657497</v>
+        <v>657491</v>
       </c>
       <c r="R99" t="n">
-        <v>6629103</v>
+        <v>6629142</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11375,12 +11375,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11644,10 +11644,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132393776</v>
+        <v>132396920</v>
       </c>
       <c r="B102" t="n">
-        <v>101304</v>
+        <v>4775</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,37 +11655,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657575</v>
+        <v>657583</v>
       </c>
       <c r="R102" t="n">
-        <v>6629232</v>
+        <v>6629810</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11712,21 +11717,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11735,26 +11730,46 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B103" t="n">
-        <v>4775</v>
+        <v>101304</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11762,42 +11777,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R103" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11824,11 +11834,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11837,36 +11857,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12096,32 +12096,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393761</v>
+        <v>132393766</v>
       </c>
       <c r="B106" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657545</v>
+        <v>657539</v>
       </c>
       <c r="R106" t="n">
-        <v>6629427</v>
+        <v>6629301</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12203,7 +12203,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132393766</v>
+        <v>132393751</v>
       </c>
       <c r="B107" t="n">
         <v>91892</v>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657539</v>
+        <v>657577</v>
       </c>
       <c r="R107" t="n">
-        <v>6629301</v>
+        <v>6629624</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393751</v>
+        <v>132393761</v>
       </c>
       <c r="B108" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657577</v>
+        <v>657545</v>
       </c>
       <c r="R108" t="n">
-        <v>6629624</v>
+        <v>6629427</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132229117</v>
+        <v>132229129</v>
       </c>
       <c r="B12" t="n">
-        <v>97338</v>
+        <v>92615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657592</v>
+        <v>657617</v>
       </c>
       <c r="R12" t="n">
-        <v>6629803</v>
+        <v>6629722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132229129</v>
+        <v>132229117</v>
       </c>
       <c r="B13" t="n">
-        <v>92615</v>
+        <v>97338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657617</v>
+        <v>657592</v>
       </c>
       <c r="R13" t="n">
-        <v>6629722</v>
+        <v>6629803</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,48 +2081,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B15" t="n">
-        <v>92312</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R15" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2154,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2164,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2170,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,45 +2188,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B16" t="n">
-        <v>4781</v>
+        <v>92312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R16" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2262,7 +2261,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2271,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,6 +2280,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303813</v>
+        <v>132303816</v>
       </c>
       <c r="B51" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657528</v>
+        <v>657523</v>
       </c>
       <c r="R51" t="n">
-        <v>6629154</v>
+        <v>6629179</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303816</v>
+        <v>132303823</v>
       </c>
       <c r="B52" t="n">
-        <v>92352</v>
+        <v>97338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657523</v>
+        <v>657524</v>
       </c>
       <c r="R52" t="n">
-        <v>6629179</v>
+        <v>6629112</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303823</v>
+        <v>132303793</v>
       </c>
       <c r="B53" t="n">
-        <v>97338</v>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657524</v>
+        <v>657601</v>
       </c>
       <c r="R53" t="n">
-        <v>6629112</v>
+        <v>6629629</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303834</v>
+        <v>132303813</v>
       </c>
       <c r="B54" t="n">
-        <v>4781</v>
+        <v>91892</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657418</v>
+        <v>657528</v>
       </c>
       <c r="R54" t="n">
-        <v>6629221</v>
+        <v>6629154</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,10 +6372,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303793</v>
+        <v>132303834</v>
       </c>
       <c r="B55" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657601</v>
+        <v>657418</v>
       </c>
       <c r="R55" t="n">
-        <v>6629629</v>
+        <v>6629221</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -9670,10 +9670,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B85" t="n">
-        <v>92547</v>
+        <v>106222</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,26 +9681,27 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9708,10 +9709,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R85" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9755,31 +9756,6 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9903,10 +9879,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132398283</v>
+        <v>132397799</v>
       </c>
       <c r="B87" t="n">
-        <v>106222</v>
+        <v>92547</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9914,27 +9890,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9942,10 +9917,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657575</v>
+        <v>657535</v>
       </c>
       <c r="R87" t="n">
-        <v>6629279</v>
+        <v>6629432</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9989,6 +9964,31 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11644,10 +11644,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B102" t="n">
-        <v>4775</v>
+        <v>101304</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,42 +11655,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R102" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11717,11 +11712,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11730,46 +11735,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132393776</v>
+        <v>132396920</v>
       </c>
       <c r="B103" t="n">
-        <v>101304</v>
+        <v>4775</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11777,37 +11762,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657575</v>
+        <v>657583</v>
       </c>
       <c r="R103" t="n">
-        <v>6629232</v>
+        <v>6629810</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11834,21 +11824,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11857,16 +11837,36 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -14280,45 +14280,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132400284</v>
+        <v>132400291</v>
       </c>
       <c r="B125" t="n">
-        <v>8444</v>
+        <v>91892</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657490</v>
+        <v>657534</v>
       </c>
       <c r="R125" t="n">
-        <v>6629140</v>
+        <v>6629757</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,7 +14353,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14360,7 +14363,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14620,48 +14628,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132400291</v>
+        <v>132400284</v>
       </c>
       <c r="B128" t="n">
-        <v>91892</v>
+        <v>8444</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>657534</v>
+        <v>657490</v>
       </c>
       <c r="R128" t="n">
-        <v>6629757</v>
+        <v>6629140</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14693,7 +14698,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14703,12 +14708,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD128" t="b">

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -2081,45 +2081,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B15" t="n">
-        <v>4781</v>
+        <v>92312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R15" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2154,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2164,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,6 +2173,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,48 +2192,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B16" t="n">
-        <v>92312</v>
+        <v>4781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R16" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2271,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -6479,32 +6479,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132303797</v>
+        <v>132303791</v>
       </c>
       <c r="B56" t="n">
-        <v>92117</v>
+        <v>4781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1106</v>
+        <v>102306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>657663</v>
+        <v>657605</v>
       </c>
       <c r="R56" t="n">
-        <v>6629597</v>
+        <v>6629850</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6586,32 +6586,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132303791</v>
+        <v>132303797</v>
       </c>
       <c r="B57" t="n">
-        <v>4781</v>
+        <v>92117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102306</v>
+        <v>1106</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657605</v>
+        <v>657663</v>
       </c>
       <c r="R57" t="n">
-        <v>6629850</v>
+        <v>6629597</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7224,7 +7224,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303802</v>
+        <v>132303801</v>
       </c>
       <c r="B63" t="n">
         <v>57945</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>657568</v>
+        <v>657607</v>
       </c>
       <c r="R63" t="n">
-        <v>6629349</v>
+        <v>6629402</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7336,7 +7336,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132303801</v>
+        <v>132303802</v>
       </c>
       <c r="B64" t="n">
         <v>57945</v>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>657607</v>
+        <v>657568</v>
       </c>
       <c r="R64" t="n">
-        <v>6629402</v>
+        <v>6629349</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8897,51 +8897,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132398009</v>
+        <v>132393767</v>
       </c>
       <c r="B78" t="n">
-        <v>91855</v>
+        <v>97338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657441</v>
+        <v>657539</v>
       </c>
       <c r="R78" t="n">
-        <v>6629193</v>
+        <v>6629272</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8968,98 +8965,91 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132393767</v>
+        <v>132395803</v>
       </c>
       <c r="B79" t="n">
-        <v>97338</v>
+        <v>97658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657539</v>
+        <v>657653</v>
       </c>
       <c r="R79" t="n">
-        <v>6629272</v>
+        <v>6629952</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9086,21 +9076,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9109,26 +9089,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132395803</v>
+        <v>132398009</v>
       </c>
       <c r="B80" t="n">
-        <v>97658</v>
+        <v>91855</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9136,27 +9121,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2326</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9164,10 +9148,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>657653</v>
+        <v>657441</v>
       </c>
       <c r="R80" t="n">
-        <v>6629952</v>
+        <v>6629193</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,12 +9192,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -11644,10 +11644,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132393776</v>
+        <v>132396920</v>
       </c>
       <c r="B102" t="n">
-        <v>101304</v>
+        <v>4775</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,37 +11655,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657575</v>
+        <v>657583</v>
       </c>
       <c r="R102" t="n">
-        <v>6629232</v>
+        <v>6629810</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11712,21 +11717,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11735,26 +11730,46 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B103" t="n">
-        <v>4775</v>
+        <v>101304</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11762,42 +11777,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R103" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11824,11 +11834,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11837,36 +11857,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12096,32 +12096,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393766</v>
+        <v>132393761</v>
       </c>
       <c r="B106" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657539</v>
+        <v>657545</v>
       </c>
       <c r="R106" t="n">
-        <v>6629301</v>
+        <v>6629427</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12203,7 +12203,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132393751</v>
+        <v>132393766</v>
       </c>
       <c r="B107" t="n">
         <v>91892</v>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657577</v>
+        <v>657539</v>
       </c>
       <c r="R107" t="n">
-        <v>6629624</v>
+        <v>6629301</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393761</v>
+        <v>132393751</v>
       </c>
       <c r="B108" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657545</v>
+        <v>657577</v>
       </c>
       <c r="R108" t="n">
-        <v>6629427</v>
+        <v>6629624</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>132082680</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>132229124</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132229123</v>
       </c>
       <c r="B6" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>132229115</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>132229139</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132229129</v>
+        <v>132229125</v>
       </c>
       <c r="B12" t="n">
-        <v>92615</v>
+        <v>57946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657617</v>
+        <v>657566</v>
       </c>
       <c r="R12" t="n">
-        <v>6629722</v>
+        <v>6629737</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,7 +1870,7 @@
         <v>132229117</v>
       </c>
       <c r="B13" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132229125</v>
+        <v>132229129</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>92621</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657566</v>
+        <v>657617</v>
       </c>
       <c r="R14" t="n">
-        <v>6629737</v>
+        <v>6629722</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,12 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,48 +2081,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B15" t="n">
-        <v>92312</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R15" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2154,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2164,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2170,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,45 +2188,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B16" t="n">
-        <v>4781</v>
+        <v>92318</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R16" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2262,7 +2261,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2271,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,6 +2280,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132229131</v>
+        <v>132229113</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657670</v>
+        <v>657681</v>
       </c>
       <c r="R17" t="n">
-        <v>6629756</v>
+        <v>6629873</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132229113</v>
+        <v>132229131</v>
       </c>
       <c r="B18" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657681</v>
+        <v>657670</v>
       </c>
       <c r="R18" t="n">
-        <v>6629873</v>
+        <v>6629756</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,7 +2516,7 @@
         <v>132229110</v>
       </c>
       <c r="B19" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>132229112</v>
       </c>
       <c r="B20" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>132229122</v>
       </c>
       <c r="B22" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132229104</v>
       </c>
       <c r="B23" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132229106</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,32 +3151,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132229135</v>
+        <v>132229105</v>
       </c>
       <c r="B25" t="n">
-        <v>4781</v>
+        <v>97346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>657669</v>
+        <v>657629</v>
       </c>
       <c r="R25" t="n">
-        <v>6629815</v>
+        <v>6629952</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3258,32 +3258,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132229105</v>
+        <v>132229135</v>
       </c>
       <c r="B26" t="n">
-        <v>97338</v>
+        <v>4781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>657629</v>
+        <v>657669</v>
       </c>
       <c r="R26" t="n">
-        <v>6629952</v>
+        <v>6629815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3368,7 @@
         <v>132229107</v>
       </c>
       <c r="B27" t="n">
-        <v>91663</v>
+        <v>91669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>132229118</v>
       </c>
       <c r="B28" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303827</v>
+        <v>132303809</v>
       </c>
       <c r="B29" t="n">
-        <v>91892</v>
+        <v>92621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657470</v>
+        <v>657556</v>
       </c>
       <c r="R29" t="n">
-        <v>6629072</v>
+        <v>6629205</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303809</v>
+        <v>132303827</v>
       </c>
       <c r="B30" t="n">
-        <v>92615</v>
+        <v>91898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657556</v>
+        <v>657470</v>
       </c>
       <c r="R30" t="n">
-        <v>6629205</v>
+        <v>6629072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3796,7 +3796,7 @@
         <v>132303818</v>
       </c>
       <c r="B31" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>132303832</v>
       </c>
       <c r="B34" t="n">
-        <v>92316</v>
+        <v>92322</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>132303803</v>
       </c>
       <c r="B35" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>132303822</v>
       </c>
       <c r="B36" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>132303789</v>
       </c>
       <c r="B37" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>132303821</v>
       </c>
       <c r="B38" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132303815</v>
       </c>
       <c r="B39" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>132303810</v>
       </c>
       <c r="B41" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132303817</v>
+        <v>132303785</v>
       </c>
       <c r="B42" t="n">
-        <v>92352</v>
+        <v>97346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657521</v>
+        <v>657626</v>
       </c>
       <c r="R42" t="n">
-        <v>6629192</v>
+        <v>6629945</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5078,10 +5078,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132303833</v>
+        <v>132303817</v>
       </c>
       <c r="B43" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>657443</v>
+        <v>657521</v>
       </c>
       <c r="R43" t="n">
-        <v>6629220</v>
+        <v>6629192</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132303785</v>
+        <v>132303794</v>
       </c>
       <c r="B44" t="n">
-        <v>97338</v>
+        <v>57946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657626</v>
+        <v>657621</v>
       </c>
       <c r="R44" t="n">
-        <v>6629945</v>
+        <v>6629620</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5265,7 +5265,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5292,32 +5297,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132303794</v>
+        <v>132303833</v>
       </c>
       <c r="B45" t="n">
-        <v>57945</v>
+        <v>92358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5327,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657621</v>
+        <v>657443</v>
       </c>
       <c r="R45" t="n">
-        <v>6629620</v>
+        <v>6629220</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5362,7 +5367,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5372,12 +5377,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132303808</v>
+        <v>132303787</v>
       </c>
       <c r="B46" t="n">
-        <v>97338</v>
+        <v>57946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>657538</v>
+        <v>657613</v>
       </c>
       <c r="R46" t="n">
-        <v>6629210</v>
+        <v>6629894</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5484,7 +5484,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5511,10 +5516,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132303787</v>
+        <v>132303808</v>
       </c>
       <c r="B47" t="n">
-        <v>57945</v>
+        <v>97346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5522,21 +5527,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5546,10 +5551,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>657613</v>
+        <v>657538</v>
       </c>
       <c r="R47" t="n">
-        <v>6629894</v>
+        <v>6629210</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5581,7 +5586,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5591,12 +5596,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5733,7 +5733,7 @@
         <v>132303819</v>
       </c>
       <c r="B49" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>132303804</v>
       </c>
       <c r="B50" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5944,32 +5944,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303816</v>
+        <v>132303793</v>
       </c>
       <c r="B51" t="n">
-        <v>92352</v>
+        <v>5199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657523</v>
+        <v>657601</v>
       </c>
       <c r="R51" t="n">
-        <v>6629179</v>
+        <v>6629629</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,10 +6051,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303823</v>
+        <v>132303813</v>
       </c>
       <c r="B52" t="n">
-        <v>97338</v>
+        <v>91898</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6062,21 +6062,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657524</v>
+        <v>657528</v>
       </c>
       <c r="R52" t="n">
-        <v>6629112</v>
+        <v>6629154</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303793</v>
+        <v>132303816</v>
       </c>
       <c r="B53" t="n">
-        <v>5199</v>
+        <v>92358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657601</v>
+        <v>657523</v>
       </c>
       <c r="R53" t="n">
-        <v>6629629</v>
+        <v>6629179</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,10 +6265,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303813</v>
+        <v>132303823</v>
       </c>
       <c r="B54" t="n">
-        <v>91892</v>
+        <v>97346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6276,21 +6276,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657528</v>
+        <v>657524</v>
       </c>
       <c r="R54" t="n">
-        <v>6629154</v>
+        <v>6629112</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6479,32 +6479,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132303791</v>
+        <v>132303797</v>
       </c>
       <c r="B56" t="n">
-        <v>4781</v>
+        <v>92123</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102306</v>
+        <v>1106</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>657605</v>
+        <v>657663</v>
       </c>
       <c r="R56" t="n">
-        <v>6629850</v>
+        <v>6629597</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6586,32 +6586,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132303797</v>
+        <v>132303791</v>
       </c>
       <c r="B57" t="n">
-        <v>92117</v>
+        <v>4781</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1106</v>
+        <v>102306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657663</v>
+        <v>657605</v>
       </c>
       <c r="R57" t="n">
-        <v>6629597</v>
+        <v>6629850</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,7 +6696,7 @@
         <v>132303835</v>
       </c>
       <c r="B58" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>132303828</v>
       </c>
       <c r="B61" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>132303805</v>
       </c>
       <c r="B62" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7224,32 +7224,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303801</v>
+        <v>132303792</v>
       </c>
       <c r="B63" t="n">
-        <v>57945</v>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7262,7 +7262,7 @@
         <v>657607</v>
       </c>
       <c r="R63" t="n">
-        <v>6629402</v>
+        <v>6629839</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7304,12 +7304,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7339,7 +7334,7 @@
         <v>132303802</v>
       </c>
       <c r="B64" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7448,32 +7443,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303792</v>
+        <v>132303801</v>
       </c>
       <c r="B65" t="n">
-        <v>4781</v>
+        <v>57946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7486,7 +7481,7 @@
         <v>657607</v>
       </c>
       <c r="R65" t="n">
-        <v>6629839</v>
+        <v>6629402</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7513,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7523,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,7 +7558,7 @@
         <v>132303826</v>
       </c>
       <c r="B66" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>132303800</v>
       </c>
       <c r="B67" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132303814</v>
       </c>
       <c r="B68" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7876,32 +7876,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132303786</v>
+        <v>132303784</v>
       </c>
       <c r="B69" t="n">
-        <v>57945</v>
+        <v>4781</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>657626</v>
+        <v>657636</v>
       </c>
       <c r="R69" t="n">
-        <v>6629917</v>
+        <v>6629952</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7956,12 +7956,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hackmärken äldre</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7988,10 +7983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132303796</v>
+        <v>132303786</v>
       </c>
       <c r="B70" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8023,10 +8018,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>657669</v>
+        <v>657626</v>
       </c>
       <c r="R70" t="n">
-        <v>6629616</v>
+        <v>6629917</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8058,7 +8053,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8068,12 +8063,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Hackmärken äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8100,10 +8095,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132303824</v>
+        <v>132303796</v>
       </c>
       <c r="B71" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8135,10 +8130,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>657521</v>
+        <v>657669</v>
       </c>
       <c r="R71" t="n">
-        <v>6629122</v>
+        <v>6629616</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8170,7 +8165,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8180,7 +8175,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8212,32 +8207,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132303784</v>
+        <v>132303824</v>
       </c>
       <c r="B72" t="n">
-        <v>4781</v>
+        <v>57946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8247,10 +8242,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>657636</v>
+        <v>657521</v>
       </c>
       <c r="R72" t="n">
-        <v>6629952</v>
+        <v>6629122</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8282,7 +8277,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8292,7 +8287,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8319,10 +8319,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132398523</v>
+        <v>132393747</v>
       </c>
       <c r="B73" t="n">
-        <v>79341</v>
+        <v>91861</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8330,40 +8330,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657569</v>
+        <v>657641</v>
       </c>
       <c r="R73" t="n">
-        <v>6629311</v>
+        <v>6629957</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8390,65 +8387,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132393747</v>
+        <v>132395560</v>
       </c>
       <c r="B74" t="n">
-        <v>91855</v>
+        <v>96446</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8456,37 +8437,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657641</v>
+        <v>657653</v>
       </c>
       <c r="R74" t="n">
-        <v>6629957</v>
+        <v>6629952</v>
       </c>
       <c r="S74" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8513,49 +8498,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132395560</v>
+        <v>132398523</v>
       </c>
       <c r="B75" t="n">
-        <v>96438</v>
+        <v>79343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8563,27 +8554,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2818</v>
+        <v>6434</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8591,10 +8581,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657653</v>
+        <v>657569</v>
       </c>
       <c r="R75" t="n">
-        <v>6629952</v>
+        <v>6629311</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8641,17 +8631,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8672,7 +8672,7 @@
         <v>132397152</v>
       </c>
       <c r="B76" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>132393759</v>
       </c>
       <c r="B77" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8897,48 +8897,52 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132393767</v>
+        <v>132395803</v>
       </c>
       <c r="B78" t="n">
-        <v>97338</v>
+        <v>97666</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657539</v>
+        <v>657653</v>
       </c>
       <c r="R78" t="n">
-        <v>6629272</v>
+        <v>6629952</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8965,21 +8969,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8988,68 +8982,69 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132395803</v>
+        <v>132393767</v>
       </c>
       <c r="B79" t="n">
-        <v>97658</v>
+        <v>97346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657653</v>
+        <v>657539</v>
       </c>
       <c r="R79" t="n">
-        <v>6629952</v>
+        <v>6629272</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9076,11 +9071,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9089,21 +9094,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9113,7 +9113,7 @@
         <v>132398009</v>
       </c>
       <c r="B80" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>132393769</v>
       </c>
       <c r="B81" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9338,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393780</v>
+        <v>132393768</v>
       </c>
       <c r="B82" t="n">
-        <v>91912</v>
+        <v>91898</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9349,19 +9349,23 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9369,10 +9373,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657500</v>
+        <v>657498</v>
       </c>
       <c r="R82" t="n">
-        <v>6629450</v>
+        <v>6629248</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9404,7 +9408,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9414,7 +9418,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9563,10 +9567,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132393768</v>
+        <v>132393780</v>
       </c>
       <c r="B84" t="n">
-        <v>91892</v>
+        <v>91918</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9574,23 +9578,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>657498</v>
+        <v>657500</v>
       </c>
       <c r="R84" t="n">
-        <v>6629248</v>
+        <v>6629450</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9670,10 +9670,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132398283</v>
+        <v>132393770</v>
       </c>
       <c r="B85" t="n">
-        <v>106222</v>
+        <v>8444</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,41 +9681,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657575</v>
+        <v>657487</v>
       </c>
       <c r="R85" t="n">
-        <v>6629279</v>
+        <v>6629134</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9742,40 +9738,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132393770</v>
+        <v>132397799</v>
       </c>
       <c r="B86" t="n">
-        <v>8444</v>
+        <v>92553</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9783,37 +9788,40 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657487</v>
+        <v>657535</v>
       </c>
       <c r="R86" t="n">
-        <v>6629134</v>
+        <v>6629432</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9840,49 +9848,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B87" t="n">
-        <v>92547</v>
+        <v>106230</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9890,26 +9914,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9917,10 +9942,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R87" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9964,31 +9989,6 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132393758</v>
+        <v>132393760</v>
       </c>
       <c r="B88" t="n">
-        <v>91892</v>
+        <v>101312</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657570</v>
+        <v>657538</v>
       </c>
       <c r="R88" t="n">
-        <v>6629495</v>
+        <v>6629429</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10115,7 +10115,7 @@
         <v>132393762</v>
       </c>
       <c r="B89" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10219,32 +10219,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132393760</v>
+        <v>132393758</v>
       </c>
       <c r="B90" t="n">
-        <v>101304</v>
+        <v>91898</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657538</v>
+        <v>657570</v>
       </c>
       <c r="R90" t="n">
-        <v>6629429</v>
+        <v>6629495</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10457,7 +10457,7 @@
         <v>132400287</v>
       </c>
       <c r="B92" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10566,37 +10566,43 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132397367</v>
+        <v>132398032</v>
       </c>
       <c r="B93" t="n">
-        <v>91814</v>
+        <v>8444</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3242</v>
+        <v>106554</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10604,10 +10610,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657627</v>
+        <v>657485</v>
       </c>
       <c r="R93" t="n">
-        <v>6629577</v>
+        <v>6629132</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10654,27 +10660,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10692,10 +10698,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132398032</v>
+        <v>132397298</v>
       </c>
       <c r="B94" t="n">
-        <v>8444</v>
+        <v>92322</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10703,32 +10709,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106554</v>
+        <v>4217</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657485</v>
+        <v>657657</v>
       </c>
       <c r="R94" t="n">
-        <v>6629132</v>
+        <v>6629610</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10786,27 +10786,27 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10824,32 +10824,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132397298</v>
+        <v>132397367</v>
       </c>
       <c r="B95" t="n">
-        <v>92316</v>
+        <v>91820</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4217</v>
+        <v>3242</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657657</v>
+        <v>657627</v>
       </c>
       <c r="R95" t="n">
-        <v>6629610</v>
+        <v>6629577</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10927,12 +10927,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10953,7 +10953,7 @@
         <v>132393772</v>
       </c>
       <c r="B96" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11057,48 +11057,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132393773</v>
+        <v>132398021</v>
       </c>
       <c r="B97" t="n">
-        <v>91892</v>
+        <v>8455</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657548</v>
+        <v>657497</v>
       </c>
       <c r="R97" t="n">
-        <v>6629166</v>
+        <v>6629177</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11125,49 +11134,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132400285</v>
+        <v>132393773</v>
       </c>
       <c r="B98" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11193,22 +11218,19 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657528</v>
+        <v>657548</v>
       </c>
       <c r="R98" t="n">
-        <v>6629248</v>
+        <v>6629166</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11237,7 +11259,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11247,12 +11269,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11261,19 +11278,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11283,7 +11299,7 @@
         <v>132400283</v>
       </c>
       <c r="B99" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11387,54 +11403,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132398021</v>
+        <v>132400285</v>
       </c>
       <c r="B100" t="n">
-        <v>8455</v>
+        <v>91898</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>657497</v>
+        <v>657528</v>
       </c>
       <c r="R100" t="n">
-        <v>6629177</v>
+        <v>6629248</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11464,9 +11474,24 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11479,77 +11504,54 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132396638</v>
+        <v>132396920</v>
       </c>
       <c r="B101" t="n">
-        <v>92191</v>
+        <v>4775</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11557,10 +11559,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657608</v>
+        <v>657583</v>
       </c>
       <c r="R101" t="n">
-        <v>6629860</v>
+        <v>6629810</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11606,7 +11608,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11619,14 +11621,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11644,10 +11641,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B102" t="n">
-        <v>4775</v>
+        <v>101312</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,42 +11652,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R102" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11717,11 +11709,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11730,84 +11732,67 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132393776</v>
+        <v>132396638</v>
       </c>
       <c r="B103" t="n">
-        <v>101304</v>
+        <v>92197</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657575</v>
+        <v>657608</v>
       </c>
       <c r="R103" t="n">
-        <v>6629232</v>
+        <v>6629860</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11834,21 +11819,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11857,26 +11832,51 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132393753</v>
+        <v>132400288</v>
       </c>
       <c r="B104" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11902,19 +11902,22 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657605</v>
+        <v>657615</v>
       </c>
       <c r="R104" t="n">
-        <v>6629627</v>
+        <v>6629610</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11956,34 +11959,40 @@
           <t>12:26</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132400288</v>
+        <v>132393753</v>
       </c>
       <c r="B105" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12009,22 +12018,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657615</v>
+        <v>657605</v>
       </c>
       <c r="R105" t="n">
-        <v>6629610</v>
+        <v>6629627</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12066,62 +12072,56 @@
           <t>12:26</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393761</v>
+        <v>132393751</v>
       </c>
       <c r="B106" t="n">
-        <v>101304</v>
+        <v>91898</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657545</v>
+        <v>657577</v>
       </c>
       <c r="R106" t="n">
-        <v>6629427</v>
+        <v>6629624</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12206,7 +12206,7 @@
         <v>132393766</v>
       </c>
       <c r="B107" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393751</v>
+        <v>132393761</v>
       </c>
       <c r="B108" t="n">
-        <v>91892</v>
+        <v>101312</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657577</v>
+        <v>657545</v>
       </c>
       <c r="R108" t="n">
-        <v>6629624</v>
+        <v>6629427</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12420,7 +12420,7 @@
         <v>132393750</v>
       </c>
       <c r="B109" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>132400294</v>
       </c>
       <c r="B110" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>132397047</v>
       </c>
       <c r="B111" t="n">
-        <v>91316</v>
+        <v>91322</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12778,60 +12778,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132397898</v>
+        <v>132393774</v>
       </c>
       <c r="B112" t="n">
-        <v>96534</v>
+        <v>91898</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657550</v>
+        <v>657579</v>
       </c>
       <c r="R112" t="n">
-        <v>6629410</v>
+        <v>6629235</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12858,103 +12846,99 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132393774</v>
+        <v>132397898</v>
       </c>
       <c r="B113" t="n">
-        <v>91892</v>
+        <v>96542</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657579</v>
+        <v>657550</v>
       </c>
       <c r="R113" t="n">
-        <v>6629235</v>
+        <v>6629410</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12981,39 +12965,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -13131,48 +13131,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132400286</v>
+        <v>132393771</v>
       </c>
       <c r="B115" t="n">
-        <v>92352</v>
+        <v>96542</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>657542</v>
+        <v>657487</v>
       </c>
       <c r="R115" t="n">
-        <v>6629285</v>
+        <v>6629135</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13211,12 +13211,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>På grannlåga</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13225,67 +13220,66 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132393771</v>
+        <v>132400286</v>
       </c>
       <c r="B116" t="n">
-        <v>96534</v>
+        <v>92358</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>657487</v>
+        <v>657542</v>
       </c>
       <c r="R116" t="n">
-        <v>6629135</v>
+        <v>6629285</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13314,7 +13308,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13324,7 +13318,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På grannlåga</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13333,18 +13332,19 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13354,7 +13354,7 @@
         <v>132400290</v>
       </c>
       <c r="B117" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13467,57 +13467,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132397930</v>
+        <v>132393764</v>
       </c>
       <c r="B118" t="n">
-        <v>4775</v>
+        <v>92358</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100299</v>
+        <v>1209</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657534</v>
+        <v>657541</v>
       </c>
       <c r="R118" t="n">
-        <v>6629364</v>
+        <v>6629301</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13544,87 +13535,71 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132397917</v>
+        <v>132397062</v>
       </c>
       <c r="B119" t="n">
-        <v>97338</v>
+        <v>96696</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13638,10 +13613,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657557</v>
+        <v>657621</v>
       </c>
       <c r="R119" t="n">
-        <v>6629386</v>
+        <v>6629728</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13688,27 +13663,7 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13726,10 +13681,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132393763</v>
+        <v>132397416</v>
       </c>
       <c r="B120" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13755,19 +13710,22 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657540</v>
+        <v>657575</v>
       </c>
       <c r="R120" t="n">
-        <v>6629314</v>
+        <v>6629496</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13794,49 +13752,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132397416</v>
+        <v>132397917</v>
       </c>
       <c r="B121" t="n">
-        <v>91892</v>
+        <v>97346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13844,26 +13818,27 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13871,10 +13846,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657575</v>
+        <v>657557</v>
       </c>
       <c r="R121" t="n">
-        <v>6629496</v>
+        <v>6629386</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13926,12 +13901,12 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -13941,7 +13916,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -13959,32 +13934,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132393764</v>
+        <v>132393763</v>
       </c>
       <c r="B122" t="n">
-        <v>92352</v>
+        <v>91898</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13994,10 +13969,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>657541</v>
+        <v>657540</v>
       </c>
       <c r="R122" t="n">
-        <v>6629301</v>
+        <v>6629314</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14029,7 +14004,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14039,7 +14014,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14069,7 +14044,7 @@
         <v>132393778</v>
       </c>
       <c r="B123" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,10 +14148,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397062</v>
+        <v>132397930</v>
       </c>
       <c r="B124" t="n">
-        <v>96688</v>
+        <v>4775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14184,27 +14159,32 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14212,10 +14192,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657621</v>
+        <v>657534</v>
       </c>
       <c r="R124" t="n">
-        <v>6629728</v>
+        <v>6629364</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14262,7 +14242,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14280,48 +14280,49 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132400291</v>
+        <v>132396661</v>
       </c>
       <c r="B125" t="n">
-        <v>91892</v>
+        <v>96446</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657534</v>
+        <v>657626</v>
       </c>
       <c r="R125" t="n">
-        <v>6629757</v>
+        <v>6629856</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14351,55 +14352,44 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132396661</v>
+        <v>132397021</v>
       </c>
       <c r="B126" t="n">
-        <v>96438</v>
+        <v>92621</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14407,27 +14397,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2818</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -14435,10 +14424,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>657626</v>
+        <v>657607</v>
       </c>
       <c r="R126" t="n">
-        <v>6629856</v>
+        <v>6629730</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14479,12 +14468,33 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14502,32 +14512,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132397021</v>
+        <v>132400291</v>
       </c>
       <c r="B127" t="n">
-        <v>92615</v>
+        <v>91898</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14536,14 +14546,14 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>657607</v>
+        <v>657534</v>
       </c>
       <c r="R127" t="n">
-        <v>6629730</v>
+        <v>6629757</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14573,9 +14583,24 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14588,40 +14613,15 @@
       <c r="AG127" t="b">
         <v>0</v>
       </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14736,10 +14736,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132396986</v>
+        <v>132393757</v>
       </c>
       <c r="B129" t="n">
-        <v>97658</v>
+        <v>5179</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14747,41 +14747,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2326</v>
+        <v>100526</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>657604</v>
+        <v>657623</v>
       </c>
       <c r="R129" t="n">
-        <v>6629772</v>
+        <v>6629491</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14808,11 +14804,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14821,21 +14827,16 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14845,7 +14846,7 @@
         <v>132396642</v>
       </c>
       <c r="B130" t="n">
-        <v>92547</v>
+        <v>92553</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14967,10 +14968,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132393757</v>
+        <v>132396986</v>
       </c>
       <c r="B131" t="n">
-        <v>5179</v>
+        <v>97666</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14978,37 +14979,41 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100526</v>
+        <v>2326</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657623</v>
+        <v>657604</v>
       </c>
       <c r="R131" t="n">
-        <v>6629491</v>
+        <v>6629772</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15035,21 +15040,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15058,16 +15053,21 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
         <v>132387913</v>
       </c>
       <c r="B132" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Alec Bailey</t>
+          <t>Alec Bailey, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -15178,7 +15178,7 @@
         <v>132388723</v>
       </c>
       <c r="B133" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>132378501</v>
       </c>
       <c r="B134" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -2081,45 +2081,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B15" t="n">
-        <v>4781</v>
+        <v>92318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R15" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2154,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2164,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,6 +2173,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,48 +2192,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B16" t="n">
-        <v>92318</v>
+        <v>4781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R16" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2271,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132229113</v>
+        <v>132229131</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657681</v>
+        <v>657670</v>
       </c>
       <c r="R17" t="n">
-        <v>6629873</v>
+        <v>6629756</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132229131</v>
+        <v>132229113</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657670</v>
+        <v>657681</v>
       </c>
       <c r="R18" t="n">
-        <v>6629756</v>
+        <v>6629873</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303809</v>
+        <v>132303827</v>
       </c>
       <c r="B29" t="n">
-        <v>92621</v>
+        <v>91898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657556</v>
+        <v>657470</v>
       </c>
       <c r="R29" t="n">
-        <v>6629205</v>
+        <v>6629072</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303827</v>
+        <v>132303818</v>
       </c>
       <c r="B30" t="n">
-        <v>91898</v>
+        <v>92358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657470</v>
+        <v>657503</v>
       </c>
       <c r="R30" t="n">
-        <v>6629072</v>
+        <v>6629178</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3793,32 +3793,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132303818</v>
+        <v>132303809</v>
       </c>
       <c r="B31" t="n">
-        <v>92358</v>
+        <v>92621</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657503</v>
+        <v>657556</v>
       </c>
       <c r="R31" t="n">
-        <v>6629178</v>
+        <v>6629205</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5944,10 +5944,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303793</v>
+        <v>132303834</v>
       </c>
       <c r="B51" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657601</v>
+        <v>657418</v>
       </c>
       <c r="R51" t="n">
-        <v>6629629</v>
+        <v>6629221</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303813</v>
+        <v>132303793</v>
       </c>
       <c r="B52" t="n">
-        <v>91898</v>
+        <v>5199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657528</v>
+        <v>657601</v>
       </c>
       <c r="R52" t="n">
-        <v>6629154</v>
+        <v>6629629</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303816</v>
+        <v>132303813</v>
       </c>
       <c r="B53" t="n">
-        <v>92358</v>
+        <v>91898</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657523</v>
+        <v>657528</v>
       </c>
       <c r="R53" t="n">
-        <v>6629179</v>
+        <v>6629154</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303823</v>
+        <v>132303816</v>
       </c>
       <c r="B54" t="n">
-        <v>97346</v>
+        <v>92358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657524</v>
+        <v>657523</v>
       </c>
       <c r="R54" t="n">
-        <v>6629112</v>
+        <v>6629179</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,32 +6372,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303834</v>
+        <v>132303823</v>
       </c>
       <c r="B55" t="n">
-        <v>4781</v>
+        <v>97346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657418</v>
+        <v>657524</v>
       </c>
       <c r="R55" t="n">
-        <v>6629221</v>
+        <v>6629112</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -9338,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393768</v>
+        <v>132393780</v>
       </c>
       <c r="B82" t="n">
-        <v>91898</v>
+        <v>91918</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9349,23 +9349,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9373,10 +9369,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657498</v>
+        <v>657500</v>
       </c>
       <c r="R82" t="n">
-        <v>6629248</v>
+        <v>6629450</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9408,7 +9404,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9418,7 +9414,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9445,53 +9441,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132396889</v>
+        <v>132393768</v>
       </c>
       <c r="B83" t="n">
-        <v>4781</v>
+        <v>91898</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657576</v>
+        <v>657498</v>
       </c>
       <c r="R83" t="n">
-        <v>6629830</v>
+        <v>6629248</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9518,11 +9509,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9531,80 +9532,69 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132393780</v>
+        <v>132396889</v>
       </c>
       <c r="B84" t="n">
-        <v>91918</v>
+        <v>4781</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>102306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>657500</v>
+        <v>657576</v>
       </c>
       <c r="R84" t="n">
-        <v>6629450</v>
+        <v>6629830</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9631,21 +9621,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9654,16 +9634,36 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11519,39 +11519,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132396920</v>
+        <v>132396638</v>
       </c>
       <c r="B101" t="n">
-        <v>4775</v>
+        <v>92197</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100299</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11559,10 +11557,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657583</v>
+        <v>657608</v>
       </c>
       <c r="R101" t="n">
-        <v>6629810</v>
+        <v>6629860</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11608,7 +11606,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11621,9 +11619,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11641,10 +11644,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132393776</v>
+        <v>132396920</v>
       </c>
       <c r="B102" t="n">
-        <v>101312</v>
+        <v>4775</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11652,37 +11655,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222498</v>
+        <v>100299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657575</v>
+        <v>657583</v>
       </c>
       <c r="R102" t="n">
-        <v>6629232</v>
+        <v>6629810</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11709,21 +11717,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11732,67 +11730,84 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132396638</v>
+        <v>132393776</v>
       </c>
       <c r="B103" t="n">
-        <v>92197</v>
+        <v>101312</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657608</v>
+        <v>657575</v>
       </c>
       <c r="R103" t="n">
-        <v>6629860</v>
+        <v>6629232</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11819,11 +11834,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11832,41 +11857,16 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -13467,48 +13467,52 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132393764</v>
+        <v>132397062</v>
       </c>
       <c r="B118" t="n">
-        <v>92358</v>
+        <v>96696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657541</v>
+        <v>657621</v>
       </c>
       <c r="R118" t="n">
-        <v>6629301</v>
+        <v>6629728</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13535,91 +13539,83 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132397062</v>
+        <v>132393764</v>
       </c>
       <c r="B119" t="n">
-        <v>96696</v>
+        <v>92358</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657621</v>
+        <v>657541</v>
       </c>
       <c r="R119" t="n">
-        <v>6629728</v>
+        <v>6629301</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13646,35 +13642,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>132082680</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>132229124</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132229123</v>
       </c>
       <c r="B6" t="n">
-        <v>92553</v>
+        <v>92563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>132229115</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>132229139</v>
       </c>
       <c r="B10" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132229125</v>
+        <v>132229129</v>
       </c>
       <c r="B12" t="n">
-        <v>57946</v>
+        <v>92631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657566</v>
+        <v>657617</v>
       </c>
       <c r="R12" t="n">
-        <v>6629737</v>
+        <v>6629722</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132229117</v>
+        <v>132229125</v>
       </c>
       <c r="B13" t="n">
-        <v>97346</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657592</v>
+        <v>657566</v>
       </c>
       <c r="R13" t="n">
-        <v>6629803</v>
+        <v>6629737</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,32 +1974,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132229129</v>
+        <v>132229117</v>
       </c>
       <c r="B14" t="n">
-        <v>92621</v>
+        <v>97356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657617</v>
+        <v>657592</v>
       </c>
       <c r="R14" t="n">
-        <v>6629722</v>
+        <v>6629803</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,48 +2081,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B15" t="n">
-        <v>92318</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R15" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2154,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2164,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2170,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2192,45 +2188,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B16" t="n">
-        <v>4781</v>
+        <v>92328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R16" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2262,7 +2261,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2272,7 +2271,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2281,6 +2280,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132229110</v>
+        <v>132229112</v>
       </c>
       <c r="B19" t="n">
-        <v>97346</v>
+        <v>91908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,21 +2524,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657640</v>
+        <v>657675</v>
       </c>
       <c r="R19" t="n">
-        <v>6629986</v>
+        <v>6629888</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132229112</v>
+        <v>132229110</v>
       </c>
       <c r="B20" t="n">
-        <v>91898</v>
+        <v>97356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657675</v>
+        <v>657640</v>
       </c>
       <c r="R20" t="n">
-        <v>6629888</v>
+        <v>6629986</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,7 +2837,7 @@
         <v>132229122</v>
       </c>
       <c r="B22" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132229104</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>132229106</v>
       </c>
       <c r="B24" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>132229105</v>
       </c>
       <c r="B25" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>132229107</v>
       </c>
       <c r="B27" t="n">
-        <v>91669</v>
+        <v>91679</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>132229118</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>132303827</v>
       </c>
       <c r="B29" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>132303818</v>
       </c>
       <c r="B30" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>132303809</v>
       </c>
       <c r="B31" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>132303832</v>
       </c>
       <c r="B34" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>132303803</v>
       </c>
       <c r="B35" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>132303822</v>
       </c>
       <c r="B36" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>132303789</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>132303821</v>
       </c>
       <c r="B38" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132303815</v>
       </c>
       <c r="B39" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>132303810</v>
       </c>
       <c r="B41" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>132303785</v>
       </c>
       <c r="B42" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>132303817</v>
       </c>
       <c r="B43" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5185,32 +5185,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132303794</v>
+        <v>132303833</v>
       </c>
       <c r="B44" t="n">
-        <v>57946</v>
+        <v>92368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>657621</v>
+        <v>657443</v>
       </c>
       <c r="R44" t="n">
-        <v>6629620</v>
+        <v>6629220</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5265,12 +5265,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5297,32 +5292,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132303833</v>
+        <v>132303794</v>
       </c>
       <c r="B45" t="n">
-        <v>92358</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5327,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>657443</v>
+        <v>657621</v>
       </c>
       <c r="R45" t="n">
-        <v>6629220</v>
+        <v>6629620</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5377,7 +5372,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5404,10 +5404,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132303787</v>
+        <v>132303808</v>
       </c>
       <c r="B46" t="n">
-        <v>57946</v>
+        <v>97356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5415,21 +5415,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>657613</v>
+        <v>657538</v>
       </c>
       <c r="R46" t="n">
-        <v>6629894</v>
+        <v>6629210</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5484,12 +5484,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,10 +5511,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132303808</v>
+        <v>132303787</v>
       </c>
       <c r="B47" t="n">
-        <v>97346</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,21 +5522,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5551,10 +5546,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>657538</v>
+        <v>657613</v>
       </c>
       <c r="R47" t="n">
-        <v>6629210</v>
+        <v>6629894</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5586,7 +5581,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5596,7 +5591,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5730,32 +5730,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132303819</v>
+        <v>132303804</v>
       </c>
       <c r="B49" t="n">
-        <v>91861</v>
+        <v>97356</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>657531</v>
+        <v>657546</v>
       </c>
       <c r="R49" t="n">
-        <v>6629126</v>
+        <v>6629244</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,32 +5837,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132303804</v>
+        <v>132303819</v>
       </c>
       <c r="B50" t="n">
-        <v>97346</v>
+        <v>91871</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>657546</v>
+        <v>657531</v>
       </c>
       <c r="R50" t="n">
-        <v>6629244</v>
+        <v>6629126</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6161,7 +6161,7 @@
         <v>132303813</v>
       </c>
       <c r="B53" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>132303816</v>
       </c>
       <c r="B54" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>132303823</v>
       </c>
       <c r="B55" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>132303797</v>
       </c>
       <c r="B56" t="n">
-        <v>92123</v>
+        <v>92133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>132303835</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7010,10 +7010,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132303828</v>
+        <v>132303802</v>
       </c>
       <c r="B61" t="n">
-        <v>91898</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>657472</v>
+        <v>657568</v>
       </c>
       <c r="R61" t="n">
-        <v>6629096</v>
+        <v>6629349</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7090,7 +7090,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7117,10 +7122,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132303805</v>
+        <v>132303801</v>
       </c>
       <c r="B62" t="n">
-        <v>97346</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,21 +7133,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7152,10 +7157,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>657549</v>
+        <v>657607</v>
       </c>
       <c r="R62" t="n">
-        <v>6629245</v>
+        <v>6629402</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7187,7 +7192,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7197,7 +7202,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7224,32 +7234,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303792</v>
+        <v>132303805</v>
       </c>
       <c r="B63" t="n">
-        <v>4781</v>
+        <v>97356</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7259,10 +7269,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>657607</v>
+        <v>657549</v>
       </c>
       <c r="R63" t="n">
-        <v>6629839</v>
+        <v>6629245</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7294,7 +7304,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7304,7 +7314,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7331,10 +7341,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132303802</v>
+        <v>132303828</v>
       </c>
       <c r="B64" t="n">
-        <v>57946</v>
+        <v>91908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7342,21 +7352,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7366,10 +7376,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>657568</v>
+        <v>657472</v>
       </c>
       <c r="R64" t="n">
-        <v>6629349</v>
+        <v>6629096</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7401,7 +7411,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7411,12 +7421,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7443,32 +7448,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303801</v>
+        <v>132303792</v>
       </c>
       <c r="B65" t="n">
-        <v>57946</v>
+        <v>4781</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7481,7 +7486,7 @@
         <v>657607</v>
       </c>
       <c r="R65" t="n">
-        <v>6629402</v>
+        <v>6629839</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7513,7 +7518,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7523,12 +7528,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,7 +7558,7 @@
         <v>132303826</v>
       </c>
       <c r="B66" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>132303800</v>
       </c>
       <c r="B67" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132303814</v>
       </c>
       <c r="B68" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7876,32 +7876,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132303784</v>
+        <v>132303786</v>
       </c>
       <c r="B69" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>657636</v>
+        <v>657626</v>
       </c>
       <c r="R69" t="n">
-        <v>6629952</v>
+        <v>6629917</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7956,7 +7956,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hackmärken äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7983,10 +7988,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132303786</v>
+        <v>132303796</v>
       </c>
       <c r="B70" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8018,10 +8023,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>657626</v>
+        <v>657669</v>
       </c>
       <c r="R70" t="n">
-        <v>6629917</v>
+        <v>6629616</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8053,7 +8058,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8063,12 +8068,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hackmärken äldre</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8095,10 +8100,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132303796</v>
+        <v>132303824</v>
       </c>
       <c r="B71" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8130,10 +8135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>657669</v>
+        <v>657521</v>
       </c>
       <c r="R71" t="n">
-        <v>6629616</v>
+        <v>6629122</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8165,7 +8170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8175,7 +8180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8207,32 +8212,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132303824</v>
+        <v>132303784</v>
       </c>
       <c r="B72" t="n">
-        <v>57946</v>
+        <v>4781</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8242,10 +8247,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>657521</v>
+        <v>657636</v>
       </c>
       <c r="R72" t="n">
-        <v>6629122</v>
+        <v>6629952</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8277,7 +8282,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8287,12 +8292,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8319,10 +8319,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132393747</v>
+        <v>132395560</v>
       </c>
       <c r="B73" t="n">
-        <v>91861</v>
+        <v>96456</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8330,37 +8330,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>657641</v>
+        <v>657653</v>
       </c>
       <c r="R73" t="n">
-        <v>6629957</v>
+        <v>6629952</v>
       </c>
       <c r="S73" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8387,49 +8391,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132395560</v>
+        <v>132398523</v>
       </c>
       <c r="B74" t="n">
-        <v>96446</v>
+        <v>79351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8437,27 +8447,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2818</v>
+        <v>6434</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8465,10 +8474,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>657653</v>
+        <v>657569</v>
       </c>
       <c r="R74" t="n">
-        <v>6629952</v>
+        <v>6629311</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8515,17 +8524,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8543,10 +8562,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132398523</v>
+        <v>132393747</v>
       </c>
       <c r="B75" t="n">
-        <v>79343</v>
+        <v>91871</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8554,40 +8573,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>657569</v>
+        <v>657641</v>
       </c>
       <c r="R75" t="n">
-        <v>6629311</v>
+        <v>6629957</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8614,55 +8630,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8672,7 +8672,7 @@
         <v>132397152</v>
       </c>
       <c r="B76" t="n">
-        <v>92553</v>
+        <v>92563</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>132393759</v>
       </c>
       <c r="B77" t="n">
-        <v>92553</v>
+        <v>92563</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8897,52 +8897,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132395803</v>
+        <v>132393767</v>
       </c>
       <c r="B78" t="n">
-        <v>97666</v>
+        <v>97356</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>657653</v>
+        <v>657539</v>
       </c>
       <c r="R78" t="n">
-        <v>6629952</v>
+        <v>6629272</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8969,11 +8965,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8982,69 +8988,68 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132393767</v>
+        <v>132395803</v>
       </c>
       <c r="B79" t="n">
-        <v>97346</v>
+        <v>97676</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>657539</v>
+        <v>657653</v>
       </c>
       <c r="R79" t="n">
-        <v>6629272</v>
+        <v>6629952</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9071,21 +9076,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9094,16 +9089,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9113,7 +9113,7 @@
         <v>132398009</v>
       </c>
       <c r="B80" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>132393769</v>
       </c>
       <c r="B81" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9338,10 +9338,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132393780</v>
+        <v>132393768</v>
       </c>
       <c r="B82" t="n">
-        <v>91918</v>
+        <v>91908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9349,19 +9349,23 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9369,10 +9373,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>657500</v>
+        <v>657498</v>
       </c>
       <c r="R82" t="n">
-        <v>6629450</v>
+        <v>6629248</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9404,7 +9408,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9414,7 +9418,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9441,10 +9445,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132393768</v>
+        <v>132393780</v>
       </c>
       <c r="B83" t="n">
-        <v>91898</v>
+        <v>91928</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9452,23 +9456,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657498</v>
+        <v>657500</v>
       </c>
       <c r="R83" t="n">
-        <v>6629248</v>
+        <v>6629450</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9777,10 +9777,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B86" t="n">
-        <v>92553</v>
+        <v>106241</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9788,26 +9788,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9815,10 +9816,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R86" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9862,31 +9863,6 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9903,10 +9879,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132398283</v>
+        <v>132397799</v>
       </c>
       <c r="B87" t="n">
-        <v>106230</v>
+        <v>92563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9914,27 +9890,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221144</v>
+        <v>1339</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9942,10 +9917,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657575</v>
+        <v>657535</v>
       </c>
       <c r="R87" t="n">
-        <v>6629279</v>
+        <v>6629432</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9989,6 +9964,31 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132393760</v>
+        <v>132393762</v>
       </c>
       <c r="B88" t="n">
-        <v>101312</v>
+        <v>97356</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>657538</v>
+        <v>657575</v>
       </c>
       <c r="R88" t="n">
-        <v>6629429</v>
+        <v>6629363</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132393762</v>
+        <v>132393758</v>
       </c>
       <c r="B89" t="n">
-        <v>97346</v>
+        <v>91908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657575</v>
+        <v>657570</v>
       </c>
       <c r="R89" t="n">
-        <v>6629363</v>
+        <v>6629495</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,48 +10219,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132393758</v>
+        <v>132398041</v>
       </c>
       <c r="B90" t="n">
-        <v>91898</v>
+        <v>9414</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>105076</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657570</v>
+        <v>657485</v>
       </c>
       <c r="R90" t="n">
-        <v>6629495</v>
+        <v>6629132</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10287,49 +10292,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132398041</v>
+        <v>132393760</v>
       </c>
       <c r="B91" t="n">
-        <v>9414</v>
+        <v>101323</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10337,42 +10358,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>105076</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657485</v>
+        <v>657538</v>
       </c>
       <c r="R91" t="n">
-        <v>6629132</v>
+        <v>6629429</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10399,55 +10415,39 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10457,7 +10457,7 @@
         <v>132400287</v>
       </c>
       <c r="B92" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>132397298</v>
       </c>
       <c r="B94" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>132397367</v>
       </c>
       <c r="B95" t="n">
-        <v>91820</v>
+        <v>91830</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10950,32 +10950,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132393772</v>
+        <v>132393773</v>
       </c>
       <c r="B96" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657497</v>
+        <v>657548</v>
       </c>
       <c r="R96" t="n">
-        <v>6629103</v>
+        <v>6629166</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11189,32 +11189,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132393773</v>
+        <v>132393772</v>
       </c>
       <c r="B98" t="n">
-        <v>91898</v>
+        <v>101323</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11224,10 +11224,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657548</v>
+        <v>657497</v>
       </c>
       <c r="R98" t="n">
-        <v>6629166</v>
+        <v>6629103</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11299,7 +11299,7 @@
         <v>132400283</v>
       </c>
       <c r="B99" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>132400285</v>
       </c>
       <c r="B100" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>132396638</v>
       </c>
       <c r="B101" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>132393776</v>
       </c>
       <c r="B103" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11873,10 +11873,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132400288</v>
+        <v>132393753</v>
       </c>
       <c r="B104" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11902,22 +11902,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657615</v>
+        <v>657605</v>
       </c>
       <c r="R104" t="n">
-        <v>6629610</v>
+        <v>6629627</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11959,40 +11956,34 @@
           <t>12:26</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132393753</v>
+        <v>132400288</v>
       </c>
       <c r="B105" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12018,19 +12009,22 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657605</v>
+        <v>657615</v>
       </c>
       <c r="R105" t="n">
-        <v>6629627</v>
+        <v>6629610</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12072,56 +12066,62 @@
           <t>12:26</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132393751</v>
+        <v>132393761</v>
       </c>
       <c r="B106" t="n">
-        <v>91898</v>
+        <v>101323</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12131,10 +12131,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>657577</v>
+        <v>657545</v>
       </c>
       <c r="R106" t="n">
-        <v>6629624</v>
+        <v>6629427</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12203,10 +12203,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132393766</v>
+        <v>132393751</v>
       </c>
       <c r="B107" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>657539</v>
+        <v>657577</v>
       </c>
       <c r="R107" t="n">
-        <v>6629301</v>
+        <v>6629624</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12273,7 +12273,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12310,32 +12310,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132393761</v>
+        <v>132393766</v>
       </c>
       <c r="B108" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>657545</v>
+        <v>657539</v>
       </c>
       <c r="R108" t="n">
-        <v>6629427</v>
+        <v>6629301</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12420,7 +12420,7 @@
         <v>132393750</v>
       </c>
       <c r="B109" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>132400294</v>
       </c>
       <c r="B110" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132397047</v>
+        <v>132393774</v>
       </c>
       <c r="B111" t="n">
-        <v>91322</v>
+        <v>91908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12660,48 +12660,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2008</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657618</v>
+        <v>657579</v>
       </c>
       <c r="R111" t="n">
-        <v>6629739</v>
+        <v>6629235</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12728,98 +12717,99 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132393774</v>
+        <v>132397898</v>
       </c>
       <c r="B112" t="n">
-        <v>91898</v>
+        <v>96552</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657579</v>
+        <v>657550</v>
       </c>
       <c r="R112" t="n">
-        <v>6629235</v>
+        <v>6629410</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12846,85 +12836,100 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132397898</v>
+        <v>132397047</v>
       </c>
       <c r="B113" t="n">
-        <v>96542</v>
+        <v>91332</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>210</v>
+        <v>2008</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12932,10 +12937,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>657550</v>
+        <v>657618</v>
       </c>
       <c r="R113" t="n">
-        <v>6629410</v>
+        <v>6629739</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12982,7 +12987,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -12995,14 +13000,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
         <v>132393771</v>
       </c>
       <c r="B115" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>132400286</v>
       </c>
       <c r="B116" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>132400290</v>
       </c>
       <c r="B117" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13467,10 +13467,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132397062</v>
+        <v>132397930</v>
       </c>
       <c r="B118" t="n">
-        <v>96696</v>
+        <v>4775</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13478,27 +13478,32 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13506,10 +13511,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657621</v>
+        <v>657534</v>
       </c>
       <c r="R118" t="n">
-        <v>6629728</v>
+        <v>6629364</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13556,7 +13561,27 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13577,7 +13602,7 @@
         <v>132393764</v>
       </c>
       <c r="B119" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13684,7 +13709,7 @@
         <v>132397416</v>
       </c>
       <c r="B120" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13810,7 +13835,7 @@
         <v>132397917</v>
       </c>
       <c r="B121" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13937,7 +13962,7 @@
         <v>132393763</v>
       </c>
       <c r="B122" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14044,7 +14069,7 @@
         <v>132393778</v>
       </c>
       <c r="B123" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14148,10 +14173,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397930</v>
+        <v>132397062</v>
       </c>
       <c r="B124" t="n">
-        <v>4775</v>
+        <v>96706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14159,32 +14184,27 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14192,10 +14212,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657534</v>
+        <v>657621</v>
       </c>
       <c r="R124" t="n">
-        <v>6629364</v>
+        <v>6629728</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14242,27 +14262,7 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14283,7 +14283,7 @@
         <v>132396661</v>
       </c>
       <c r="B125" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>132397021</v>
       </c>
       <c r="B126" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>132400291</v>
       </c>
       <c r="B127" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14843,10 +14843,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132396642</v>
+        <v>132396986</v>
       </c>
       <c r="B130" t="n">
-        <v>92553</v>
+        <v>97676</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14854,26 +14854,27 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1339</v>
+        <v>2326</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14881,10 +14882,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657608</v>
+        <v>657604</v>
       </c>
       <c r="R130" t="n">
-        <v>6629860</v>
+        <v>6629772</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14930,27 +14931,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -14968,10 +14949,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132396986</v>
+        <v>132396642</v>
       </c>
       <c r="B131" t="n">
-        <v>97666</v>
+        <v>92563</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14979,27 +14960,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2326</v>
+        <v>1339</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -15007,10 +14987,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657604</v>
+        <v>657608</v>
       </c>
       <c r="R131" t="n">
-        <v>6629772</v>
+        <v>6629860</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15056,7 +15036,27 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
         <v>132387913</v>
       </c>
       <c r="B132" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson</t>
+          <t>Elias Yngvesson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -15178,7 +15178,7 @@
         <v>132388723</v>
       </c>
       <c r="B133" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>132378501</v>
       </c>
       <c r="B134" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -2081,45 +2081,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132229114</v>
+        <v>132229108</v>
       </c>
       <c r="B15" t="n">
-        <v>4781</v>
+        <v>92328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657663</v>
+        <v>657630</v>
       </c>
       <c r="R15" t="n">
-        <v>6629880</v>
+        <v>6629995</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2151,7 +2154,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2164,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2170,6 +2173,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,48 +2192,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132229108</v>
+        <v>132229114</v>
       </c>
       <c r="B16" t="n">
-        <v>92328</v>
+        <v>4781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657630</v>
+        <v>657663</v>
       </c>
       <c r="R16" t="n">
-        <v>6629995</v>
+        <v>6629880</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,7 +2262,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2271,7 +2272,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2281,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132229131</v>
+        <v>132229113</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657670</v>
+        <v>657681</v>
       </c>
       <c r="R17" t="n">
-        <v>6629756</v>
+        <v>6629873</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132229113</v>
+        <v>132229131</v>
       </c>
       <c r="B18" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657681</v>
+        <v>657670</v>
       </c>
       <c r="R18" t="n">
-        <v>6629873</v>
+        <v>6629756</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3579,32 +3579,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132303827</v>
+        <v>132303809</v>
       </c>
       <c r="B29" t="n">
-        <v>91908</v>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657470</v>
+        <v>657556</v>
       </c>
       <c r="R29" t="n">
-        <v>6629072</v>
+        <v>6629205</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,32 +3686,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132303818</v>
+        <v>132303827</v>
       </c>
       <c r="B30" t="n">
-        <v>92368</v>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657503</v>
+        <v>657470</v>
       </c>
       <c r="R30" t="n">
-        <v>6629178</v>
+        <v>6629072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3793,32 +3793,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132303809</v>
+        <v>132303818</v>
       </c>
       <c r="B31" t="n">
-        <v>92631</v>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657556</v>
+        <v>657503</v>
       </c>
       <c r="R31" t="n">
-        <v>6629205</v>
+        <v>6629178</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132303836</v>
+        <v>132303811</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>657418</v>
+        <v>657543</v>
       </c>
       <c r="R32" t="n">
-        <v>6629375</v>
+        <v>6629159</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4007,10 +4007,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132303811</v>
+        <v>132303836</v>
       </c>
       <c r="B33" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>657543</v>
+        <v>657418</v>
       </c>
       <c r="R33" t="n">
-        <v>6629159</v>
+        <v>6629375</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4117,7 +4117,7 @@
         <v>132303832</v>
       </c>
       <c r="B34" t="n">
-        <v>92332</v>
+        <v>92333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>132303803</v>
       </c>
       <c r="B35" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>132303822</v>
       </c>
       <c r="B36" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>132303789</v>
       </c>
       <c r="B37" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>132303821</v>
       </c>
       <c r="B38" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>132303815</v>
       </c>
       <c r="B39" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>132303810</v>
       </c>
       <c r="B41" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>132303785</v>
       </c>
       <c r="B42" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>132303817</v>
       </c>
       <c r="B43" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>132303833</v>
       </c>
       <c r="B44" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>132303808</v>
       </c>
       <c r="B46" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132303804</v>
+        <v>132303819</v>
       </c>
       <c r="B49" t="n">
-        <v>97356</v>
+        <v>91872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>657546</v>
+        <v>657531</v>
       </c>
       <c r="R49" t="n">
-        <v>6629244</v>
+        <v>6629126</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,32 +5837,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132303819</v>
+        <v>132303804</v>
       </c>
       <c r="B50" t="n">
-        <v>91871</v>
+        <v>97357</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5872,13 +5872,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>657531</v>
+        <v>657546</v>
       </c>
       <c r="R50" t="n">
-        <v>6629126</v>
+        <v>6629244</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5944,10 +5944,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132303834</v>
+        <v>132303793</v>
       </c>
       <c r="B51" t="n">
-        <v>4781</v>
+        <v>5199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5955,21 +5955,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>657418</v>
+        <v>657601</v>
       </c>
       <c r="R51" t="n">
-        <v>6629221</v>
+        <v>6629629</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,32 +6051,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132303793</v>
+        <v>132303813</v>
       </c>
       <c r="B52" t="n">
-        <v>5199</v>
+        <v>91909</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>657601</v>
+        <v>657528</v>
       </c>
       <c r="R52" t="n">
-        <v>6629629</v>
+        <v>6629154</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,32 +6158,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132303813</v>
+        <v>132303816</v>
       </c>
       <c r="B53" t="n">
-        <v>91908</v>
+        <v>92369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>657528</v>
+        <v>657523</v>
       </c>
       <c r="R53" t="n">
-        <v>6629154</v>
+        <v>6629179</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,32 +6265,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132303816</v>
+        <v>132303823</v>
       </c>
       <c r="B54" t="n">
-        <v>92368</v>
+        <v>97357</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>657523</v>
+        <v>657524</v>
       </c>
       <c r="R54" t="n">
-        <v>6629179</v>
+        <v>6629112</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6372,32 +6372,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132303823</v>
+        <v>132303834</v>
       </c>
       <c r="B55" t="n">
-        <v>97356</v>
+        <v>4781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>657524</v>
+        <v>657418</v>
       </c>
       <c r="R55" t="n">
-        <v>6629112</v>
+        <v>6629221</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,32 +6479,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132303797</v>
+        <v>132303791</v>
       </c>
       <c r="B56" t="n">
-        <v>92133</v>
+        <v>4781</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1106</v>
+        <v>102306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>657663</v>
+        <v>657605</v>
       </c>
       <c r="R56" t="n">
-        <v>6629597</v>
+        <v>6629850</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6586,32 +6586,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132303791</v>
+        <v>132303797</v>
       </c>
       <c r="B57" t="n">
-        <v>4781</v>
+        <v>92134</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102306</v>
+        <v>1106</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6621,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>657605</v>
+        <v>657663</v>
       </c>
       <c r="R57" t="n">
-        <v>6629850</v>
+        <v>6629597</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,7 +6696,7 @@
         <v>132303835</v>
       </c>
       <c r="B58" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7234,32 +7234,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132303805</v>
+        <v>132303792</v>
       </c>
       <c r="B63" t="n">
-        <v>97356</v>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>657549</v>
+        <v>657607</v>
       </c>
       <c r="R63" t="n">
-        <v>6629245</v>
+        <v>6629839</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7344,7 +7344,7 @@
         <v>132303828</v>
       </c>
       <c r="B64" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7448,32 +7448,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132303792</v>
+        <v>132303805</v>
       </c>
       <c r="B65" t="n">
-        <v>4781</v>
+        <v>97357</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>657607</v>
+        <v>657549</v>
       </c>
       <c r="R65" t="n">
-        <v>6629839</v>
+        <v>6629245</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,7 +7558,7 @@
         <v>132303826</v>
       </c>
       <c r="B66" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>132303800</v>
       </c>
       <c r="B67" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>132303814</v>
       </c>
       <c r="B68" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>132395560</v>
       </c>
       <c r="B73" t="n">
-        <v>96456</v>
+        <v>96457</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>132393747</v>
       </c>
       <c r="B75" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>132397152</v>
       </c>
       <c r="B76" t="n">
-        <v>92563</v>
+        <v>92564</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>132393759</v>
       </c>
       <c r="B77" t="n">
-        <v>92563</v>
+        <v>92564</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>132393767</v>
       </c>
       <c r="B78" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>132395803</v>
       </c>
       <c r="B79" t="n">
-        <v>97676</v>
+        <v>97677</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>132398009</v>
       </c>
       <c r="B80" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>132393769</v>
       </c>
       <c r="B81" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>132393768</v>
       </c>
       <c r="B82" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9445,44 +9445,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132393780</v>
+        <v>132396889</v>
       </c>
       <c r="B83" t="n">
-        <v>91928</v>
+        <v>4781</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>102306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>657500</v>
+        <v>657576</v>
       </c>
       <c r="R83" t="n">
-        <v>6629450</v>
+        <v>6629830</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9509,21 +9518,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9532,69 +9531,80 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132396889</v>
+        <v>132393780</v>
       </c>
       <c r="B84" t="n">
-        <v>4781</v>
+        <v>91929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102306</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>657576</v>
+        <v>657500</v>
       </c>
       <c r="R84" t="n">
-        <v>6629830</v>
+        <v>6629450</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9621,11 +9631,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9634,46 +9654,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132393770</v>
+        <v>132397799</v>
       </c>
       <c r="B85" t="n">
-        <v>8444</v>
+        <v>92564</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9681,37 +9681,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106554</v>
+        <v>1339</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>657487</v>
+        <v>657535</v>
       </c>
       <c r="R85" t="n">
-        <v>6629134</v>
+        <v>6629432</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9738,49 +9741,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132398283</v>
+        <v>132393770</v>
       </c>
       <c r="B86" t="n">
-        <v>106241</v>
+        <v>8444</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9788,41 +9807,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>657575</v>
+        <v>657487</v>
       </c>
       <c r="R86" t="n">
-        <v>6629279</v>
+        <v>6629134</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9849,40 +9864,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132397799</v>
+        <v>132398283</v>
       </c>
       <c r="B87" t="n">
-        <v>92563</v>
+        <v>106242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9890,26 +9914,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9917,10 +9942,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>657535</v>
+        <v>657575</v>
       </c>
       <c r="R87" t="n">
-        <v>6629432</v>
+        <v>6629279</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9964,31 +9989,6 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10008,7 +10008,7 @@
         <v>132393762</v>
       </c>
       <c r="B88" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10112,48 +10112,52 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132393758</v>
+        <v>132400287</v>
       </c>
       <c r="B89" t="n">
-        <v>91908</v>
+        <v>101324</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>657570</v>
+        <v>657564</v>
       </c>
       <c r="R89" t="n">
-        <v>6629495</v>
+        <v>6629426</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10182,7 +10186,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10196,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10201,71 +10205,67 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132398041</v>
+        <v>132393758</v>
       </c>
       <c r="B90" t="n">
-        <v>9414</v>
+        <v>91909</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>105076</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>657485</v>
+        <v>657570</v>
       </c>
       <c r="R90" t="n">
-        <v>6629132</v>
+        <v>6629495</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10292,65 +10292,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132393760</v>
+        <v>132398041</v>
       </c>
       <c r="B91" t="n">
-        <v>101323</v>
+        <v>9414</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10358,37 +10342,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>105076</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>657538</v>
+        <v>657485</v>
       </c>
       <c r="R91" t="n">
-        <v>6629429</v>
+        <v>6629132</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10415,49 +10404,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132400287</v>
+        <v>132393760</v>
       </c>
       <c r="B92" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10482,24 +10487,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>657564</v>
+        <v>657538</v>
       </c>
       <c r="R92" t="n">
-        <v>6629426</v>
+        <v>6629429</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10528,7 +10529,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10538,7 +10539,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10547,29 +10548,28 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132398032</v>
+        <v>132397298</v>
       </c>
       <c r="B93" t="n">
-        <v>8444</v>
+        <v>92333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10577,32 +10577,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106554</v>
+        <v>4217</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10610,10 +10604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>657485</v>
+        <v>657657</v>
       </c>
       <c r="R93" t="n">
-        <v>6629132</v>
+        <v>6629610</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10660,27 +10654,27 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>glasbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Betula pubescens</t>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10698,32 +10692,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132397298</v>
+        <v>132397367</v>
       </c>
       <c r="B94" t="n">
-        <v>92332</v>
+        <v>91831</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4217</v>
+        <v>3242</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10736,10 +10730,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>657657</v>
+        <v>657627</v>
       </c>
       <c r="R94" t="n">
-        <v>6629610</v>
+        <v>6629577</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10801,12 +10795,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10824,37 +10818,43 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132397367</v>
+        <v>132398032</v>
       </c>
       <c r="B95" t="n">
-        <v>91830</v>
+        <v>8444</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3242</v>
+        <v>106554</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>657627</v>
+        <v>657485</v>
       </c>
       <c r="R95" t="n">
-        <v>6629577</v>
+        <v>6629132</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10912,27 +10912,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>glasbjörk</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Dead branch  # Grov nedfallen gren # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Betula pubescens</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10950,48 +10950,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132393773</v>
+        <v>132400283</v>
       </c>
       <c r="B96" t="n">
-        <v>91908</v>
+        <v>96553</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>657548</v>
+        <v>657491</v>
       </c>
       <c r="R96" t="n">
-        <v>6629166</v>
+        <v>6629142</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11045,66 +11045,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132398021</v>
+        <v>132400285</v>
       </c>
       <c r="B97" t="n">
-        <v>8455</v>
+        <v>91909</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>657497</v>
+        <v>657528</v>
       </c>
       <c r="R97" t="n">
-        <v>6629177</v>
+        <v>6629248</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11134,9 +11128,24 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11149,72 +11158,47 @@
       <c r="AG97" t="b">
         <v>0</v>
       </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132393772</v>
+        <v>132393773</v>
       </c>
       <c r="B98" t="n">
-        <v>101323</v>
+        <v>91909</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11224,10 +11208,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>657497</v>
+        <v>657548</v>
       </c>
       <c r="R98" t="n">
-        <v>6629103</v>
+        <v>6629166</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11259,7 +11243,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11269,7 +11253,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11296,10 +11280,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132400283</v>
+        <v>132398021</v>
       </c>
       <c r="B99" t="n">
-        <v>96552</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11307,34 +11291,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>657491</v>
+        <v>657497</v>
       </c>
       <c r="R99" t="n">
-        <v>6629142</v>
+        <v>6629177</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11364,90 +11357,103 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132400285</v>
+        <v>132393772</v>
       </c>
       <c r="B100" t="n">
-        <v>91908</v>
+        <v>101324</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>657528</v>
+        <v>657497</v>
       </c>
       <c r="R100" t="n">
-        <v>6629248</v>
+        <v>6629103</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11476,7 +11482,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11486,12 +11492,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11500,56 +11501,57 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132396638</v>
+        <v>132396920</v>
       </c>
       <c r="B101" t="n">
-        <v>92207</v>
+        <v>4775</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11557,10 +11559,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>657608</v>
+        <v>657583</v>
       </c>
       <c r="R101" t="n">
-        <v>6629860</v>
+        <v>6629810</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11606,7 +11608,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -11619,14 +11621,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11644,10 +11641,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132396920</v>
+        <v>132393776</v>
       </c>
       <c r="B102" t="n">
-        <v>4775</v>
+        <v>101324</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,42 +11652,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>657583</v>
+        <v>657575</v>
       </c>
       <c r="R102" t="n">
-        <v>6629810</v>
+        <v>6629232</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11717,11 +11709,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -11730,84 +11732,67 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132393776</v>
+        <v>132396638</v>
       </c>
       <c r="B103" t="n">
-        <v>101323</v>
+        <v>92208</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>657575</v>
+        <v>657608</v>
       </c>
       <c r="R103" t="n">
-        <v>6629232</v>
+        <v>6629860</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11834,21 +11819,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11857,26 +11832,51 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132393753</v>
+        <v>132400288</v>
       </c>
       <c r="B104" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11902,19 +11902,22 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>657605</v>
+        <v>657615</v>
       </c>
       <c r="R104" t="n">
-        <v>6629627</v>
+        <v>6629610</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11956,34 +11959,40 @@
           <t>12:26</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132400288</v>
+        <v>132393753</v>
       </c>
       <c r="B105" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12009,22 +12018,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>657615</v>
+        <v>657605</v>
       </c>
       <c r="R105" t="n">
-        <v>6629610</v>
+        <v>6629627</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12066,30 +12072,24 @@
           <t>12:26</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12099,7 +12099,7 @@
         <v>132393761</v>
       </c>
       <c r="B106" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>132393751</v>
       </c>
       <c r="B107" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>132393766</v>
       </c>
       <c r="B108" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12417,10 +12417,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132393750</v>
+        <v>132400294</v>
       </c>
       <c r="B109" t="n">
-        <v>57950</v>
+        <v>91929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12428,37 +12428,44 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>657622</v>
+        <v>657599</v>
       </c>
       <c r="R109" t="n">
-        <v>6629865</v>
+        <v>6629841</v>
       </c>
       <c r="S109" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12487,7 +12494,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12497,12 +12504,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12511,28 +12518,29 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132400294</v>
+        <v>132393750</v>
       </c>
       <c r="B110" t="n">
-        <v>91928</v>
+        <v>57950</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12540,44 +12548,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>657599</v>
+        <v>657622</v>
       </c>
       <c r="R110" t="n">
-        <v>6629841</v>
+        <v>6629865</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12606,7 +12607,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12616,12 +12617,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12630,67 +12631,78 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132393774</v>
+        <v>132397898</v>
       </c>
       <c r="B111" t="n">
-        <v>91908</v>
+        <v>96553</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>657579</v>
+        <v>657550</v>
       </c>
       <c r="R111" t="n">
-        <v>6629235</v>
+        <v>6629410</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12717,49 +12729,65 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132397898</v>
+        <v>132396621</v>
       </c>
       <c r="B112" t="n">
-        <v>96552</v>
+        <v>5179</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12767,35 +12795,32 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12803,10 +12828,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>657550</v>
+        <v>657605</v>
       </c>
       <c r="R112" t="n">
-        <v>6629410</v>
+        <v>6629877</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12847,33 +12872,12 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -12894,7 +12898,7 @@
         <v>132397047</v>
       </c>
       <c r="B113" t="n">
-        <v>91332</v>
+        <v>91333</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13020,57 +13024,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132396621</v>
+        <v>132393774</v>
       </c>
       <c r="B114" t="n">
-        <v>5179</v>
+        <v>91909</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>657605</v>
+        <v>657579</v>
       </c>
       <c r="R114" t="n">
-        <v>6629877</v>
+        <v>6629235</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13097,11 +13092,21 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13110,69 +13115,64 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132393771</v>
+        <v>132400286</v>
       </c>
       <c r="B115" t="n">
-        <v>96552</v>
+        <v>92369</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>657487</v>
+        <v>657542</v>
       </c>
       <c r="R115" t="n">
-        <v>6629135</v>
+        <v>6629285</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13211,7 +13211,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På grannlåga</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13220,66 +13225,67 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132400286</v>
+        <v>132393771</v>
       </c>
       <c r="B116" t="n">
-        <v>92368</v>
+        <v>96553</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>657542</v>
+        <v>657487</v>
       </c>
       <c r="R116" t="n">
-        <v>6629285</v>
+        <v>6629135</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13308,7 +13314,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13318,12 +13324,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På grannlåga</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13332,19 +13333,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13354,7 +13354,7 @@
         <v>132400290</v>
       </c>
       <c r="B117" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13467,43 +13467,38 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132397930</v>
+        <v>132397917</v>
       </c>
       <c r="B118" t="n">
-        <v>4775</v>
+        <v>97357</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13511,10 +13506,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>657534</v>
+        <v>657557</v>
       </c>
       <c r="R118" t="n">
-        <v>6629364</v>
+        <v>6629386</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13566,12 +13561,12 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -13581,7 +13576,7 @@
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13599,48 +13594,52 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132393764</v>
+        <v>132397062</v>
       </c>
       <c r="B119" t="n">
-        <v>92368</v>
+        <v>96707</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>657541</v>
+        <v>657621</v>
       </c>
       <c r="R119" t="n">
-        <v>6629301</v>
+        <v>6629728</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13667,90 +13666,83 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132397416</v>
+        <v>132393764</v>
       </c>
       <c r="B120" t="n">
-        <v>91908</v>
+        <v>92369</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>657575</v>
+        <v>657541</v>
       </c>
       <c r="R120" t="n">
-        <v>6629496</v>
+        <v>6629301</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13777,65 +13769,49 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132397917</v>
+        <v>132397416</v>
       </c>
       <c r="B121" t="n">
-        <v>97356</v>
+        <v>91909</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13843,27 +13819,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13871,10 +13846,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>657557</v>
+        <v>657575</v>
       </c>
       <c r="R121" t="n">
-        <v>6629386</v>
+        <v>6629496</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13926,12 +13901,12 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -13941,7 +13916,7 @@
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -13962,7 +13937,7 @@
         <v>132393763</v>
       </c>
       <c r="B122" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14069,7 +14044,7 @@
         <v>132393778</v>
       </c>
       <c r="B123" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,10 +14148,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132397062</v>
+        <v>132397930</v>
       </c>
       <c r="B124" t="n">
-        <v>96706</v>
+        <v>4775</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14184,27 +14159,32 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14212,10 +14192,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>657621</v>
+        <v>657534</v>
       </c>
       <c r="R124" t="n">
-        <v>6629728</v>
+        <v>6629364</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14262,7 +14242,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14280,49 +14280,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132396661</v>
+        <v>132400291</v>
       </c>
       <c r="B125" t="n">
-        <v>96456</v>
+        <v>91909</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Rosenlund, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>657626</v>
+        <v>657534</v>
       </c>
       <c r="R125" t="n">
-        <v>6629856</v>
+        <v>6629757</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14352,44 +14351,55 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>Alsumpskog</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132397021</v>
+        <v>132400284</v>
       </c>
       <c r="B126" t="n">
-        <v>92631</v>
+        <v>8444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14397,37 +14407,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>106554</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Åttondelen, Upl</t>
+          <t>Tvärorna, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>657607</v>
+        <v>657490</v>
       </c>
       <c r="R126" t="n">
-        <v>6629730</v>
+        <v>6629140</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14457,9 +14464,19 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14472,88 +14489,64 @@
       <c r="AG126" t="b">
         <v>0</v>
       </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
+          <t>Malva Gradstock</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>132400291</v>
+        <v>132396661</v>
       </c>
       <c r="B127" t="n">
-        <v>91908</v>
+        <v>96457</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rosenlund, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>657534</v>
+        <v>657626</v>
       </c>
       <c r="R127" t="n">
-        <v>6629757</v>
+        <v>6629856</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14583,55 +14576,44 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>på granlåga</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>Alsumpskog</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132400284</v>
+        <v>132397021</v>
       </c>
       <c r="B128" t="n">
-        <v>8444</v>
+        <v>92632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14639,34 +14621,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106554</v>
+        <v>3298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Tvärorna, Upl</t>
+          <t>Åttondelen, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>657490</v>
+        <v>657607</v>
       </c>
       <c r="R128" t="n">
-        <v>6629140</v>
+        <v>6629730</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14696,19 +14681,9 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14721,15 +14696,40 @@
       <c r="AG128" t="b">
         <v>0</v>
       </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Malva Gradstock</t>
+          <t>Alec Bailey, Elias Yngvesson, Tomas Falk, Malva Gradstock</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132396986</v>
+        <v>132396642</v>
       </c>
       <c r="B130" t="n">
-        <v>97676</v>
+        <v>92564</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14854,27 +14854,26 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2326</v>
+        <v>1339</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -14882,10 +14881,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>657604</v>
+        <v>657608</v>
       </c>
       <c r="R130" t="n">
-        <v>6629772</v>
+        <v>6629860</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14931,7 +14930,27 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Alsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -14949,10 +14968,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132396642</v>
+        <v>132396986</v>
       </c>
       <c r="B131" t="n">
-        <v>92563</v>
+        <v>97677</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14960,26 +14979,27 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1339</v>
+        <v>2326</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14987,10 +15007,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>657608</v>
+        <v>657604</v>
       </c>
       <c r="R131" t="n">
-        <v>6629860</v>
+        <v>6629772</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15036,27 +15056,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Alsumpskog</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15077,7 +15077,7 @@
         <v>132387913</v>
       </c>
       <c r="B132" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>132388723</v>
       </c>
       <c r="B133" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>132378501</v>
       </c>
       <c r="B134" t="n">
-        <v>97356</v>
+        <v>97357</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AZ154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229105</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229117</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303785</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303803</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303804</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303808</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303821</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303823</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132378501</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393762</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393767</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393787</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397917</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393771</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2743,6 +2838,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397898</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2850,6 +2950,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400283</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396638</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082690</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3207,6 +3322,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082696</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3314,6 +3434,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303797</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3430,6 +3555,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082688</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3537,6 +3667,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229112</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3644,6 +3779,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229118</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3751,6 +3891,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303813</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3858,6 +4003,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303827</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3965,6 +4115,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303828</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4072,6 +4227,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303837</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4179,6 +4339,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393751</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4286,6 +4451,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393758</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4393,6 +4563,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393763</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4500,6 +4675,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393766</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4607,6 +4787,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393768</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4714,6 +4899,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393773</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4821,6 +5011,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393774</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4928,6 +5123,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393789</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5054,6 +5254,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397416</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5170,6 +5375,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400285</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5286,6 +5496,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400290</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5402,6 +5617,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400291</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5513,6 +5733,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400292</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5629,6 +5854,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082692</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5736,6 +5966,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303800</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5843,6 +6078,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303814</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5950,6 +6190,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303815</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6057,6 +6302,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303816</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6164,6 +6414,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303817</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6271,6 +6526,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303818</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6378,6 +6638,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303833</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6485,6 +6750,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393753</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6592,6 +6862,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393764</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6699,6 +6974,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393769</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6806,6 +7086,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393778</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6913,6 +7198,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393783</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7026,6 +7316,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400286</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7142,6 +7437,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400288</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7249,6 +7549,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229123</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7356,6 +7661,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393759</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7481,6 +7791,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396642</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7602,6 +7917,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397152</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7728,6 +8048,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397799</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7857,6 +8182,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397047</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7964,6 +8294,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397062</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8070,6 +8405,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132395803</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8176,6 +8516,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396986</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8283,6 +8628,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303790</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8390,6 +8740,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303807</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8507,6 +8862,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132395560</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8613,6 +8973,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396661</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8739,6 +9104,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397734</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8865,6 +9235,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397928</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8972,6 +9347,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229107</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9098,6 +9478,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397367</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9205,6 +9590,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229129</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9312,6 +9702,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303809</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9438,6 +9833,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397021</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9550,6 +9950,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303832</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9676,6 +10081,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397298</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9783,6 +10193,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229122</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9890,6 +10305,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303782</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9987,6 +10407,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130158974</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10103,6 +10528,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082694</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10210,6 +10640,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229106</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10317,6 +10752,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229126</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10424,6 +10864,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303819</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10531,6 +10976,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393747</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10652,6 +11102,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398009</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10778,6 +11233,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398523</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10890,6 +11350,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229115</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11002,6 +11467,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229124</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11114,6 +11584,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229125</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11226,6 +11701,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229139</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11338,6 +11818,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303786</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11450,6 +11935,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303787</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11562,6 +12052,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303794</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11674,6 +12169,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303796</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11786,6 +12286,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303801</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11898,6 +12403,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303802</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12010,6 +12520,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303824</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12122,6 +12637,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303840</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12234,6 +12754,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393750</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12356,6 +12881,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396920</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12488,6 +13018,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132397930</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12595,6 +13130,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082678</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12702,6 +13242,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303788</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12809,6 +13354,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303799</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12916,6 +13466,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303838</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13023,6 +13578,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393757</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13134,6 +13694,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396621</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13241,6 +13806,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393788</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13373,6 +13943,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398722</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13480,6 +14055,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229114</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13587,6 +14167,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229127</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13694,6 +14279,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229130</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13801,6 +14391,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229131</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13908,6 +14503,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229132</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14015,6 +14615,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229135</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14122,6 +14727,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229138</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14229,6 +14839,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303784</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14336,6 +14951,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303791</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14443,6 +15063,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303792</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14550,6 +15175,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303798</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14657,6 +15287,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303830</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14764,6 +15399,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303834</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14871,6 +15511,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303836</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14993,6 +15638,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132396889</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15121,6 +15771,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398041</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15228,6 +15883,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229113</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15335,6 +15995,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303793</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15442,6 +16107,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303811</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15549,6 +16219,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303839</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15681,6 +16356,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398021</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15788,6 +16468,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229128</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15895,6 +16580,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393770</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16027,6 +16717,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398032</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16135,6 +16830,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400284</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16237,6 +16937,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398283</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16344,6 +17049,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303810</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16451,6 +17161,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132303826</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16552,6 +17267,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132387913</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16654,6 +17374,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132388723</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16761,6 +17486,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393760</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16868,6 +17598,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393761</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16975,6 +17710,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393772</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17082,6 +17822,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393776</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17194,6 +17939,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132400287</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17305,6 +18055,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132229108</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17416,6 +18171,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132082680</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17537,6 +18297,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398263</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17658,8 +18423,168 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132398561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -18066,7 +18066,7 @@
         <v>132082680</v>
       </c>
       <c r="B152" t="n">
-        <v>91993</v>
+        <v>92035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 5455-2025 artfynd.xlsx
+++ b/artfynd/A 5455-2025 artfynd.xlsx
@@ -18066,7 +18066,7 @@
         <v>132082680</v>
       </c>
       <c r="B152" t="n">
-        <v>92035</v>
+        <v>92062</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
